--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553039</v>
+        <v>124553000</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504635</v>
+        <v>504774</v>
       </c>
       <c r="R29" t="n">
-        <v>6612001</v>
+        <v>6611972</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553034</v>
+        <v>124553040</v>
       </c>
       <c r="B30" t="n">
         <v>105676</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504683</v>
+        <v>504638</v>
       </c>
       <c r="R30" t="n">
-        <v>6611983</v>
+        <v>6611981</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4224,7 +4224,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553000</v>
+        <v>124553037</v>
       </c>
       <c r="B31" t="n">
         <v>105676</v>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4268,13 +4268,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504774</v>
+        <v>504667</v>
       </c>
       <c r="R31" t="n">
-        <v>6611972</v>
+        <v>6611989</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,10 +4335,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553011</v>
+        <v>124553014</v>
       </c>
       <c r="B32" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4347,27 +4347,23 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>1</t>
@@ -4379,10 +4375,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504726</v>
+        <v>504725</v>
       </c>
       <c r="R32" t="n">
-        <v>6611959</v>
+        <v>6611991</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4419,7 +4415,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4428,6 +4424,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4557,7 +4554,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553042</v>
+        <v>124553043</v>
       </c>
       <c r="B34" t="n">
         <v>105676</v>
@@ -4601,10 +4598,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504630</v>
+        <v>504644</v>
       </c>
       <c r="R34" t="n">
-        <v>6611972</v>
+        <v>6611959</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4668,10 +4665,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553014</v>
+        <v>124553031</v>
       </c>
       <c r="B35" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4680,26 +4677,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4708,10 +4709,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504725</v>
+        <v>504697</v>
       </c>
       <c r="R35" t="n">
-        <v>6611991</v>
+        <v>6612016</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4748,7 +4749,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4757,7 +4758,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4776,7 +4776,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553030</v>
+        <v>124553032</v>
       </c>
       <c r="B36" t="n">
         <v>105676</v>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504720</v>
+        <v>504686</v>
       </c>
       <c r="R36" t="n">
-        <v>6612011</v>
+        <v>6611987</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4887,10 +4887,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553010</v>
+        <v>124553015</v>
       </c>
       <c r="B37" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4899,20 +4899,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504732</v>
+        <v>504740</v>
       </c>
       <c r="R37" t="n">
-        <v>6611958</v>
+        <v>6612008</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4967,6 +4967,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4993,7 +4998,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553037</v>
+        <v>124553036</v>
       </c>
       <c r="B38" t="n">
         <v>105676</v>
@@ -5028,7 +5033,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5040,7 +5045,7 @@
         <v>504667</v>
       </c>
       <c r="R38" t="n">
-        <v>6611989</v>
+        <v>6611981</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5077,7 +5082,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5104,7 +5109,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553012</v>
+        <v>124553035</v>
       </c>
       <c r="B39" t="n">
         <v>105676</v>
@@ -5148,10 +5153,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504726</v>
+        <v>504665</v>
       </c>
       <c r="R39" t="n">
-        <v>6611974</v>
+        <v>6611970</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5188,7 +5193,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5215,7 +5220,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553032</v>
+        <v>124553016</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5250,7 +5255,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5259,10 +5264,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504686</v>
+        <v>504741</v>
       </c>
       <c r="R40" t="n">
-        <v>6611987</v>
+        <v>6612008</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5299,7 +5304,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5326,7 +5331,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553035</v>
+        <v>124553002</v>
       </c>
       <c r="B41" t="n">
         <v>105676</v>
@@ -5370,10 +5375,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504665</v>
+        <v>504759</v>
       </c>
       <c r="R41" t="n">
-        <v>6611970</v>
+        <v>6611991</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5410,7 +5415,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5437,7 +5442,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553040</v>
+        <v>124553011</v>
       </c>
       <c r="B42" t="n">
         <v>105676</v>
@@ -5472,7 +5477,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5481,10 +5486,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504638</v>
+        <v>504726</v>
       </c>
       <c r="R42" t="n">
-        <v>6611981</v>
+        <v>6611959</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5521,7 +5526,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5548,7 +5553,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553043</v>
+        <v>124553013</v>
       </c>
       <c r="B43" t="n">
         <v>105676</v>
@@ -5583,7 +5588,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5592,10 +5597,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504644</v>
+        <v>504727</v>
       </c>
       <c r="R43" t="n">
-        <v>6611959</v>
+        <v>6611975</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5632,7 +5637,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5659,7 +5664,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553015</v>
+        <v>124553039</v>
       </c>
       <c r="B44" t="n">
         <v>105676</v>
@@ -5694,7 +5699,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5703,10 +5708,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504740</v>
+        <v>504635</v>
       </c>
       <c r="R44" t="n">
-        <v>6612008</v>
+        <v>6612001</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5743,7 +5748,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5770,7 +5775,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553031</v>
+        <v>124553038</v>
       </c>
       <c r="B45" t="n">
         <v>105676</v>
@@ -5805,7 +5810,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5814,10 +5819,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504697</v>
+        <v>504663</v>
       </c>
       <c r="R45" t="n">
-        <v>6612016</v>
+        <v>6611991</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5854,7 +5859,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5881,7 +5886,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553036</v>
+        <v>124553042</v>
       </c>
       <c r="B46" t="n">
         <v>105676</v>
@@ -5916,7 +5921,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5925,10 +5930,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504667</v>
+        <v>504630</v>
       </c>
       <c r="R46" t="n">
-        <v>6611981</v>
+        <v>6611972</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5965,7 +5970,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5992,7 +5997,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553013</v>
+        <v>124553034</v>
       </c>
       <c r="B47" t="n">
         <v>105676</v>
@@ -6027,7 +6032,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6036,10 +6041,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504727</v>
+        <v>504683</v>
       </c>
       <c r="R47" t="n">
-        <v>6611975</v>
+        <v>6611983</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6076,7 +6081,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6103,7 +6108,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553002</v>
+        <v>124553005</v>
       </c>
       <c r="B48" t="n">
         <v>105676</v>
@@ -6147,10 +6152,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504759</v>
+        <v>504746</v>
       </c>
       <c r="R48" t="n">
-        <v>6611991</v>
+        <v>6611972</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6187,7 +6192,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6214,7 +6219,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553005</v>
+        <v>124553033</v>
       </c>
       <c r="B49" t="n">
         <v>105676</v>
@@ -6249,7 +6254,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6258,10 +6263,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504746</v>
+        <v>504688</v>
       </c>
       <c r="R49" t="n">
-        <v>6611972</v>
+        <v>6611985</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6298,7 +6303,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6325,7 +6330,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553033</v>
+        <v>124553017</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6360,7 +6365,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6369,10 +6374,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504688</v>
+        <v>504749</v>
       </c>
       <c r="R50" t="n">
-        <v>6611985</v>
+        <v>6612014</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6409,7 +6414,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6436,10 +6441,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553003</v>
+        <v>124553010</v>
       </c>
       <c r="B51" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6448,20 +6453,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6471,7 +6476,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6480,10 +6485,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504753</v>
+        <v>504732</v>
       </c>
       <c r="R51" t="n">
-        <v>6611982</v>
+        <v>6611958</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6516,11 +6521,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6547,7 +6547,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553038</v>
+        <v>124553012</v>
       </c>
       <c r="B52" t="n">
         <v>105676</v>
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504663</v>
+        <v>504726</v>
       </c>
       <c r="R52" t="n">
-        <v>6611991</v>
+        <v>6611974</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6658,7 +6658,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553016</v>
+        <v>124553030</v>
       </c>
       <c r="B53" t="n">
         <v>105676</v>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504741</v>
+        <v>504720</v>
       </c>
       <c r="R53" t="n">
-        <v>6612008</v>
+        <v>6612011</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553017</v>
+        <v>124553003</v>
       </c>
       <c r="B54" t="n">
         <v>105676</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504749</v>
+        <v>504753</v>
       </c>
       <c r="R54" t="n">
-        <v>6612014</v>
+        <v>6611982</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553000</v>
+        <v>124553004</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504774</v>
+        <v>504750</v>
       </c>
       <c r="R29" t="n">
-        <v>6611972</v>
+        <v>6611973</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553040</v>
+        <v>124553034</v>
       </c>
       <c r="B30" t="n">
         <v>105676</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504638</v>
+        <v>504683</v>
       </c>
       <c r="R30" t="n">
-        <v>6611981</v>
+        <v>6611983</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4224,7 +4224,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553037</v>
+        <v>124553031</v>
       </c>
       <c r="B31" t="n">
         <v>105676</v>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504667</v>
+        <v>504697</v>
       </c>
       <c r="R31" t="n">
-        <v>6611989</v>
+        <v>6612016</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,10 +4335,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553014</v>
+        <v>124553039</v>
       </c>
       <c r="B32" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4347,26 +4347,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4375,10 +4379,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504725</v>
+        <v>504635</v>
       </c>
       <c r="R32" t="n">
-        <v>6611991</v>
+        <v>6612001</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4415,7 +4419,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4424,7 +4428,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4443,7 +4446,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553004</v>
+        <v>124553000</v>
       </c>
       <c r="B33" t="n">
         <v>105676</v>
@@ -4478,7 +4481,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4487,13 +4490,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504750</v>
+        <v>504774</v>
       </c>
       <c r="R33" t="n">
-        <v>6611973</v>
+        <v>6611972</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4527,7 +4530,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4554,7 +4557,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553043</v>
+        <v>124553015</v>
       </c>
       <c r="B34" t="n">
         <v>105676</v>
@@ -4589,7 +4592,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4598,10 +4601,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504644</v>
+        <v>504740</v>
       </c>
       <c r="R34" t="n">
-        <v>6611959</v>
+        <v>6612008</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4638,7 +4641,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4665,7 +4668,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553031</v>
+        <v>124553036</v>
       </c>
       <c r="B35" t="n">
         <v>105676</v>
@@ -4700,7 +4703,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4709,10 +4712,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504697</v>
+        <v>504667</v>
       </c>
       <c r="R35" t="n">
-        <v>6612016</v>
+        <v>6611981</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4749,7 +4752,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4776,7 +4779,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553032</v>
+        <v>124553011</v>
       </c>
       <c r="B36" t="n">
         <v>105676</v>
@@ -4811,7 +4814,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4820,10 +4823,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504686</v>
+        <v>504726</v>
       </c>
       <c r="R36" t="n">
-        <v>6611987</v>
+        <v>6611959</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4860,7 +4863,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4887,7 +4890,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553015</v>
+        <v>124553043</v>
       </c>
       <c r="B37" t="n">
         <v>105676</v>
@@ -4922,7 +4925,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4931,10 +4934,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504740</v>
+        <v>504644</v>
       </c>
       <c r="R37" t="n">
-        <v>6612008</v>
+        <v>6611959</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4971,7 +4974,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4998,7 +5001,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553036</v>
+        <v>124553005</v>
       </c>
       <c r="B38" t="n">
         <v>105676</v>
@@ -5042,10 +5045,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504667</v>
+        <v>504746</v>
       </c>
       <c r="R38" t="n">
-        <v>6611981</v>
+        <v>6611972</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5082,7 +5085,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5109,7 +5112,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553035</v>
+        <v>124553012</v>
       </c>
       <c r="B39" t="n">
         <v>105676</v>
@@ -5153,10 +5156,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504665</v>
+        <v>504726</v>
       </c>
       <c r="R39" t="n">
-        <v>6611970</v>
+        <v>6611974</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5193,7 +5196,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5220,7 +5223,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553016</v>
+        <v>124553042</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5255,7 +5258,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5264,10 +5267,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504741</v>
+        <v>504630</v>
       </c>
       <c r="R40" t="n">
-        <v>6612008</v>
+        <v>6611972</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5304,7 +5307,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5331,7 +5334,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553002</v>
+        <v>124553017</v>
       </c>
       <c r="B41" t="n">
         <v>105676</v>
@@ -5375,10 +5378,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504759</v>
+        <v>504749</v>
       </c>
       <c r="R41" t="n">
-        <v>6611991</v>
+        <v>6612014</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5415,7 +5418,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5442,7 +5445,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553011</v>
+        <v>124553002</v>
       </c>
       <c r="B42" t="n">
         <v>105676</v>
@@ -5486,10 +5489,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504726</v>
+        <v>504759</v>
       </c>
       <c r="R42" t="n">
-        <v>6611959</v>
+        <v>6611991</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5526,7 +5529,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5553,7 +5556,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553013</v>
+        <v>124553037</v>
       </c>
       <c r="B43" t="n">
         <v>105676</v>
@@ -5588,7 +5591,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5597,10 +5600,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504727</v>
+        <v>504667</v>
       </c>
       <c r="R43" t="n">
-        <v>6611975</v>
+        <v>6611989</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5637,7 +5640,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5664,7 +5667,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553039</v>
+        <v>124553016</v>
       </c>
       <c r="B44" t="n">
         <v>105676</v>
@@ -5708,10 +5711,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504635</v>
+        <v>504741</v>
       </c>
       <c r="R44" t="n">
-        <v>6612001</v>
+        <v>6612008</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5748,7 +5751,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5775,7 +5778,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553038</v>
+        <v>124553003</v>
       </c>
       <c r="B45" t="n">
         <v>105676</v>
@@ -5810,7 +5813,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5819,10 +5822,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504663</v>
+        <v>504753</v>
       </c>
       <c r="R45" t="n">
-        <v>6611991</v>
+        <v>6611982</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5859,7 +5862,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5886,10 +5889,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553042</v>
+        <v>124553010</v>
       </c>
       <c r="B46" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5898,20 +5901,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5921,7 +5924,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5930,10 +5933,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504630</v>
+        <v>504732</v>
       </c>
       <c r="R46" t="n">
-        <v>6611972</v>
+        <v>6611958</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5966,11 +5969,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5997,7 +5995,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553034</v>
+        <v>124553032</v>
       </c>
       <c r="B47" t="n">
         <v>105676</v>
@@ -6032,7 +6030,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6041,10 +6039,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504683</v>
+        <v>504686</v>
       </c>
       <c r="R47" t="n">
-        <v>6611983</v>
+        <v>6611987</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6081,7 +6079,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6108,7 +6106,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553005</v>
+        <v>124553030</v>
       </c>
       <c r="B48" t="n">
         <v>105676</v>
@@ -6143,7 +6141,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6152,10 +6150,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504746</v>
+        <v>504720</v>
       </c>
       <c r="R48" t="n">
-        <v>6611972</v>
+        <v>6612011</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6192,7 +6190,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6219,7 +6217,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553033</v>
+        <v>124553038</v>
       </c>
       <c r="B49" t="n">
         <v>105676</v>
@@ -6254,7 +6252,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6263,10 +6261,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504688</v>
+        <v>504663</v>
       </c>
       <c r="R49" t="n">
-        <v>6611985</v>
+        <v>6611991</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6303,7 +6301,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6330,7 +6328,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553017</v>
+        <v>124553035</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6374,10 +6372,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504749</v>
+        <v>504665</v>
       </c>
       <c r="R50" t="n">
-        <v>6612014</v>
+        <v>6611970</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6414,7 +6412,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6441,10 +6439,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553010</v>
+        <v>124553013</v>
       </c>
       <c r="B51" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6453,20 +6451,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6485,10 +6483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504732</v>
+        <v>504727</v>
       </c>
       <c r="R51" t="n">
-        <v>6611958</v>
+        <v>6611975</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6521,6 +6519,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6547,7 +6550,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553012</v>
+        <v>124553040</v>
       </c>
       <c r="B52" t="n">
         <v>105676</v>
@@ -6582,7 +6585,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6591,10 +6594,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504726</v>
+        <v>504638</v>
       </c>
       <c r="R52" t="n">
-        <v>6611974</v>
+        <v>6611981</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6631,7 +6634,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6658,7 +6661,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553030</v>
+        <v>124553033</v>
       </c>
       <c r="B53" t="n">
         <v>105676</v>
@@ -6693,7 +6696,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6702,10 +6705,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504720</v>
+        <v>504688</v>
       </c>
       <c r="R53" t="n">
-        <v>6612011</v>
+        <v>6611985</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6742,7 +6745,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6769,10 +6772,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553003</v>
+        <v>124553014</v>
       </c>
       <c r="B54" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6781,30 +6784,26 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6812,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504753</v>
+        <v>504725</v>
       </c>
       <c r="R54" t="n">
-        <v>6611982</v>
+        <v>6611991</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6852,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6862,6 +6861,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553004</v>
+        <v>124553013</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504750</v>
+        <v>504727</v>
       </c>
       <c r="R29" t="n">
-        <v>6611973</v>
+        <v>6611975</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4335,7 +4335,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553039</v>
+        <v>124553002</v>
       </c>
       <c r="B32" t="n">
         <v>105676</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504635</v>
+        <v>504759</v>
       </c>
       <c r="R32" t="n">
-        <v>6612001</v>
+        <v>6611991</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,7 +4446,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553000</v>
+        <v>124553033</v>
       </c>
       <c r="B33" t="n">
         <v>105676</v>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4490,13 +4490,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504774</v>
+        <v>504688</v>
       </c>
       <c r="R33" t="n">
-        <v>6611972</v>
+        <v>6611985</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4557,7 +4557,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553015</v>
+        <v>124553030</v>
       </c>
       <c r="B34" t="n">
         <v>105676</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504740</v>
+        <v>504720</v>
       </c>
       <c r="R34" t="n">
-        <v>6612008</v>
+        <v>6612011</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4668,7 +4668,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553036</v>
+        <v>124553042</v>
       </c>
       <c r="B35" t="n">
         <v>105676</v>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504667</v>
+        <v>504630</v>
       </c>
       <c r="R35" t="n">
-        <v>6611981</v>
+        <v>6611972</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4779,7 +4779,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553011</v>
+        <v>124553040</v>
       </c>
       <c r="B36" t="n">
         <v>105676</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504726</v>
+        <v>504638</v>
       </c>
       <c r="R36" t="n">
-        <v>6611959</v>
+        <v>6611981</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4890,7 +4890,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553043</v>
+        <v>124553037</v>
       </c>
       <c r="B37" t="n">
         <v>105676</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504644</v>
+        <v>504667</v>
       </c>
       <c r="R37" t="n">
-        <v>6611959</v>
+        <v>6611989</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5001,7 +5001,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553005</v>
+        <v>124553003</v>
       </c>
       <c r="B38" t="n">
         <v>105676</v>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504746</v>
+        <v>504753</v>
       </c>
       <c r="R38" t="n">
-        <v>6611972</v>
+        <v>6611982</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5112,7 +5112,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553012</v>
+        <v>124553017</v>
       </c>
       <c r="B39" t="n">
         <v>105676</v>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504726</v>
+        <v>504749</v>
       </c>
       <c r="R39" t="n">
-        <v>6611974</v>
+        <v>6612014</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5223,7 +5223,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553042</v>
+        <v>124553011</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504630</v>
+        <v>504726</v>
       </c>
       <c r="R40" t="n">
-        <v>6611972</v>
+        <v>6611959</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5334,7 +5334,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553017</v>
+        <v>124553043</v>
       </c>
       <c r="B41" t="n">
         <v>105676</v>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504749</v>
+        <v>504644</v>
       </c>
       <c r="R41" t="n">
-        <v>6612014</v>
+        <v>6611959</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5445,7 +5445,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553002</v>
+        <v>124553005</v>
       </c>
       <c r="B42" t="n">
         <v>105676</v>
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504759</v>
+        <v>504746</v>
       </c>
       <c r="R42" t="n">
-        <v>6611991</v>
+        <v>6611972</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5556,10 +5556,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553037</v>
+        <v>124553014</v>
       </c>
       <c r="B43" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5568,30 +5568,26 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5600,10 +5596,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504667</v>
+        <v>504725</v>
       </c>
       <c r="R43" t="n">
-        <v>6611989</v>
+        <v>6611991</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5640,7 +5636,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5649,6 +5645,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5667,10 +5664,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553016</v>
+        <v>124553010</v>
       </c>
       <c r="B44" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5679,20 +5676,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5702,7 +5699,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5711,10 +5708,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504741</v>
+        <v>504732</v>
       </c>
       <c r="R44" t="n">
-        <v>6612008</v>
+        <v>6611958</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5747,11 +5744,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5778,7 +5770,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553003</v>
+        <v>124553016</v>
       </c>
       <c r="B45" t="n">
         <v>105676</v>
@@ -5813,7 +5805,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5822,10 +5814,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504753</v>
+        <v>504741</v>
       </c>
       <c r="R45" t="n">
-        <v>6611982</v>
+        <v>6612008</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5862,7 +5854,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5889,10 +5881,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553010</v>
+        <v>124553012</v>
       </c>
       <c r="B46" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5901,20 +5893,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5933,10 +5925,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504732</v>
+        <v>504726</v>
       </c>
       <c r="R46" t="n">
-        <v>6611958</v>
+        <v>6611974</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5969,6 +5961,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5995,7 +5992,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553032</v>
+        <v>124553038</v>
       </c>
       <c r="B47" t="n">
         <v>105676</v>
@@ -6030,7 +6027,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6039,10 +6036,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504686</v>
+        <v>504663</v>
       </c>
       <c r="R47" t="n">
-        <v>6611987</v>
+        <v>6611991</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6079,7 +6076,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6106,7 +6103,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553030</v>
+        <v>124553035</v>
       </c>
       <c r="B48" t="n">
         <v>105676</v>
@@ -6141,7 +6138,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6150,10 +6147,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504720</v>
+        <v>504665</v>
       </c>
       <c r="R48" t="n">
-        <v>6612011</v>
+        <v>6611970</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6190,7 +6187,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6217,7 +6214,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553038</v>
+        <v>124553015</v>
       </c>
       <c r="B49" t="n">
         <v>105676</v>
@@ -6261,10 +6258,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504663</v>
+        <v>504740</v>
       </c>
       <c r="R49" t="n">
-        <v>6611991</v>
+        <v>6612008</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6301,7 +6298,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6328,7 +6325,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553035</v>
+        <v>124553036</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6372,10 +6369,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504665</v>
+        <v>504667</v>
       </c>
       <c r="R50" t="n">
-        <v>6611970</v>
+        <v>6611981</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6412,7 +6409,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6439,7 +6436,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553013</v>
+        <v>124553004</v>
       </c>
       <c r="B51" t="n">
         <v>105676</v>
@@ -6483,10 +6480,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504727</v>
+        <v>504750</v>
       </c>
       <c r="R51" t="n">
-        <v>6611975</v>
+        <v>6611973</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6523,7 +6520,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6550,7 +6547,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553040</v>
+        <v>124553039</v>
       </c>
       <c r="B52" t="n">
         <v>105676</v>
@@ -6585,7 +6582,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6594,10 +6591,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504638</v>
+        <v>504635</v>
       </c>
       <c r="R52" t="n">
-        <v>6611981</v>
+        <v>6612001</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6634,7 +6631,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6661,7 +6658,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553033</v>
+        <v>124553000</v>
       </c>
       <c r="B53" t="n">
         <v>105676</v>
@@ -6696,7 +6693,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6705,13 +6702,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504688</v>
+        <v>504774</v>
       </c>
       <c r="R53" t="n">
-        <v>6611985</v>
+        <v>6611972</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6745,7 +6742,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6772,10 +6769,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553014</v>
+        <v>124553032</v>
       </c>
       <c r="B54" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6784,26 +6781,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6812,10 +6813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504725</v>
+        <v>504686</v>
       </c>
       <c r="R54" t="n">
-        <v>6611991</v>
+        <v>6611987</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6852,7 +6853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6861,7 +6862,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553013</v>
+        <v>124553037</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504727</v>
+        <v>504667</v>
       </c>
       <c r="R29" t="n">
-        <v>6611975</v>
+        <v>6611989</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553034</v>
+        <v>124553032</v>
       </c>
       <c r="B30" t="n">
         <v>105676</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504683</v>
+        <v>504686</v>
       </c>
       <c r="R30" t="n">
-        <v>6611983</v>
+        <v>6611987</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4224,7 +4224,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553031</v>
+        <v>124553035</v>
       </c>
       <c r="B31" t="n">
         <v>105676</v>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504697</v>
+        <v>504665</v>
       </c>
       <c r="R31" t="n">
-        <v>6612016</v>
+        <v>6611970</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,7 +4335,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553002</v>
+        <v>124553031</v>
       </c>
       <c r="B32" t="n">
         <v>105676</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504759</v>
+        <v>504697</v>
       </c>
       <c r="R32" t="n">
-        <v>6611991</v>
+        <v>6612016</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,7 +4446,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553033</v>
+        <v>124553030</v>
       </c>
       <c r="B33" t="n">
         <v>105676</v>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504688</v>
+        <v>504720</v>
       </c>
       <c r="R33" t="n">
-        <v>6611985</v>
+        <v>6612011</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4557,7 +4557,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553030</v>
+        <v>124553003</v>
       </c>
       <c r="B34" t="n">
         <v>105676</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504720</v>
+        <v>504753</v>
       </c>
       <c r="R34" t="n">
-        <v>6612011</v>
+        <v>6611982</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4668,10 +4668,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553042</v>
+        <v>124553010</v>
       </c>
       <c r="B35" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4680,20 +4680,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504630</v>
+        <v>504732</v>
       </c>
       <c r="R35" t="n">
-        <v>6611972</v>
+        <v>6611958</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4748,11 +4748,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4779,7 +4774,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553040</v>
+        <v>124553039</v>
       </c>
       <c r="B36" t="n">
         <v>105676</v>
@@ -4814,7 +4809,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4823,10 +4818,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504638</v>
+        <v>504635</v>
       </c>
       <c r="R36" t="n">
-        <v>6611981</v>
+        <v>6612001</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4863,7 +4858,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4890,7 +4885,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553037</v>
+        <v>124553042</v>
       </c>
       <c r="B37" t="n">
         <v>105676</v>
@@ -4925,7 +4920,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4934,10 +4929,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504667</v>
+        <v>504630</v>
       </c>
       <c r="R37" t="n">
-        <v>6611989</v>
+        <v>6611972</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4974,7 +4969,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5001,7 +4996,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553003</v>
+        <v>124553034</v>
       </c>
       <c r="B38" t="n">
         <v>105676</v>
@@ -5036,7 +5031,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5045,10 +5040,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504753</v>
+        <v>504683</v>
       </c>
       <c r="R38" t="n">
-        <v>6611982</v>
+        <v>6611983</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5085,7 +5080,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5112,7 +5107,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553017</v>
+        <v>124553043</v>
       </c>
       <c r="B39" t="n">
         <v>105676</v>
@@ -5147,7 +5142,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5156,10 +5151,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504749</v>
+        <v>504644</v>
       </c>
       <c r="R39" t="n">
-        <v>6612014</v>
+        <v>6611959</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5196,7 +5191,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5223,7 +5218,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553011</v>
+        <v>124553002</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5267,10 +5262,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504726</v>
+        <v>504759</v>
       </c>
       <c r="R40" t="n">
-        <v>6611959</v>
+        <v>6611991</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5307,7 +5302,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5334,7 +5329,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553043</v>
+        <v>124553038</v>
       </c>
       <c r="B41" t="n">
         <v>105676</v>
@@ -5369,7 +5364,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5378,10 +5373,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504644</v>
+        <v>504663</v>
       </c>
       <c r="R41" t="n">
-        <v>6611959</v>
+        <v>6611991</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5418,7 +5413,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5445,7 +5440,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553005</v>
+        <v>124553036</v>
       </c>
       <c r="B42" t="n">
         <v>105676</v>
@@ -5489,10 +5484,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504746</v>
+        <v>504667</v>
       </c>
       <c r="R42" t="n">
-        <v>6611972</v>
+        <v>6611981</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5529,7 +5524,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5556,10 +5551,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553014</v>
+        <v>124553000</v>
       </c>
       <c r="B43" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5568,26 +5563,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5596,13 +5595,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504725</v>
+        <v>504774</v>
       </c>
       <c r="R43" t="n">
-        <v>6611991</v>
+        <v>6611972</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5636,7 +5635,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5645,7 +5644,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5664,10 +5662,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553010</v>
+        <v>124553017</v>
       </c>
       <c r="B44" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5676,20 +5674,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5708,10 +5706,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504732</v>
+        <v>504749</v>
       </c>
       <c r="R44" t="n">
-        <v>6611958</v>
+        <v>6612014</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5744,6 +5742,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5881,7 +5884,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553012</v>
+        <v>124553005</v>
       </c>
       <c r="B46" t="n">
         <v>105676</v>
@@ -5925,10 +5928,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504726</v>
+        <v>504746</v>
       </c>
       <c r="R46" t="n">
-        <v>6611974</v>
+        <v>6611972</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5992,7 +5995,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553038</v>
+        <v>124553011</v>
       </c>
       <c r="B47" t="n">
         <v>105676</v>
@@ -6036,10 +6039,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504663</v>
+        <v>504726</v>
       </c>
       <c r="R47" t="n">
-        <v>6611991</v>
+        <v>6611959</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6076,7 +6079,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6103,7 +6106,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553035</v>
+        <v>124553040</v>
       </c>
       <c r="B48" t="n">
         <v>105676</v>
@@ -6138,7 +6141,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6147,10 +6150,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504665</v>
+        <v>504638</v>
       </c>
       <c r="R48" t="n">
-        <v>6611970</v>
+        <v>6611981</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6187,7 +6190,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6214,7 +6217,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553015</v>
+        <v>124553012</v>
       </c>
       <c r="B49" t="n">
         <v>105676</v>
@@ -6258,10 +6261,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504740</v>
+        <v>504726</v>
       </c>
       <c r="R49" t="n">
-        <v>6612008</v>
+        <v>6611974</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6298,7 +6301,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6325,7 +6328,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553036</v>
+        <v>124553004</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6369,10 +6372,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504667</v>
+        <v>504750</v>
       </c>
       <c r="R50" t="n">
-        <v>6611981</v>
+        <v>6611973</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6409,7 +6412,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6436,7 +6439,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553004</v>
+        <v>124553015</v>
       </c>
       <c r="B51" t="n">
         <v>105676</v>
@@ -6480,10 +6483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504750</v>
+        <v>504740</v>
       </c>
       <c r="R51" t="n">
-        <v>6611973</v>
+        <v>6612008</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6520,7 +6523,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6547,10 +6550,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553039</v>
+        <v>124553014</v>
       </c>
       <c r="B52" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6559,30 +6562,26 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6591,10 +6590,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504635</v>
+        <v>504725</v>
       </c>
       <c r="R52" t="n">
-        <v>6612001</v>
+        <v>6611991</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6631,7 +6630,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6640,6 +6639,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6658,7 +6658,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553000</v>
+        <v>124553013</v>
       </c>
       <c r="B53" t="n">
         <v>105676</v>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6702,13 +6702,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504774</v>
+        <v>504727</v>
       </c>
       <c r="R53" t="n">
-        <v>6611972</v>
+        <v>6611975</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553032</v>
+        <v>124553033</v>
       </c>
       <c r="B54" t="n">
         <v>105676</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504686</v>
+        <v>504688</v>
       </c>
       <c r="R54" t="n">
-        <v>6611987</v>
+        <v>6611985</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -6328,7 +6328,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553004</v>
+        <v>124553015</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504750</v>
+        <v>504740</v>
       </c>
       <c r="R50" t="n">
-        <v>6611973</v>
+        <v>6612008</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6439,7 +6439,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553015</v>
+        <v>124553004</v>
       </c>
       <c r="B51" t="n">
         <v>105676</v>
@@ -6483,10 +6483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504740</v>
+        <v>504750</v>
       </c>
       <c r="R51" t="n">
-        <v>6612008</v>
+        <v>6611973</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553037</v>
+        <v>124553017</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504667</v>
+        <v>504749</v>
       </c>
       <c r="R29" t="n">
-        <v>6611989</v>
+        <v>6612014</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553032</v>
+        <v>124553033</v>
       </c>
       <c r="B30" t="n">
         <v>105676</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504686</v>
+        <v>504688</v>
       </c>
       <c r="R30" t="n">
-        <v>6611987</v>
+        <v>6611985</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4224,7 +4224,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553035</v>
+        <v>124553004</v>
       </c>
       <c r="B31" t="n">
         <v>105676</v>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504665</v>
+        <v>504750</v>
       </c>
       <c r="R31" t="n">
-        <v>6611970</v>
+        <v>6611973</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,7 +4335,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553031</v>
+        <v>124553011</v>
       </c>
       <c r="B32" t="n">
         <v>105676</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504697</v>
+        <v>504726</v>
       </c>
       <c r="R32" t="n">
-        <v>6612016</v>
+        <v>6611959</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,7 +4446,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553030</v>
+        <v>124553036</v>
       </c>
       <c r="B33" t="n">
         <v>105676</v>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504720</v>
+        <v>504667</v>
       </c>
       <c r="R33" t="n">
-        <v>6612011</v>
+        <v>6611981</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4557,7 +4557,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553003</v>
+        <v>124553035</v>
       </c>
       <c r="B34" t="n">
         <v>105676</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504753</v>
+        <v>504665</v>
       </c>
       <c r="R34" t="n">
-        <v>6611982</v>
+        <v>6611970</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4668,10 +4668,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553010</v>
+        <v>124553034</v>
       </c>
       <c r="B35" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4680,20 +4680,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504732</v>
+        <v>504683</v>
       </c>
       <c r="R35" t="n">
-        <v>6611958</v>
+        <v>6611983</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4748,6 +4748,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4774,7 +4779,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553039</v>
+        <v>124553016</v>
       </c>
       <c r="B36" t="n">
         <v>105676</v>
@@ -4818,10 +4823,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504635</v>
+        <v>504741</v>
       </c>
       <c r="R36" t="n">
-        <v>6612001</v>
+        <v>6612008</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4858,7 +4863,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4885,7 +4890,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553042</v>
+        <v>124553039</v>
       </c>
       <c r="B37" t="n">
         <v>105676</v>
@@ -4920,7 +4925,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4929,10 +4934,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504630</v>
+        <v>504635</v>
       </c>
       <c r="R37" t="n">
-        <v>6611972</v>
+        <v>6612001</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4996,7 +5001,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553034</v>
+        <v>124553005</v>
       </c>
       <c r="B38" t="n">
         <v>105676</v>
@@ -5031,7 +5036,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5040,10 +5045,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504683</v>
+        <v>504746</v>
       </c>
       <c r="R38" t="n">
-        <v>6611983</v>
+        <v>6611972</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5080,7 +5085,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5107,7 +5112,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553043</v>
+        <v>124553040</v>
       </c>
       <c r="B39" t="n">
         <v>105676</v>
@@ -5142,7 +5147,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5151,10 +5156,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504644</v>
+        <v>504638</v>
       </c>
       <c r="R39" t="n">
-        <v>6611959</v>
+        <v>6611981</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5191,7 +5196,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5218,7 +5223,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553002</v>
+        <v>124553030</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5253,7 +5258,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5262,10 +5267,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504759</v>
+        <v>504720</v>
       </c>
       <c r="R40" t="n">
-        <v>6611991</v>
+        <v>6612011</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5302,7 +5307,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5329,10 +5334,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553038</v>
+        <v>124553014</v>
       </c>
       <c r="B41" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5341,27 +5346,23 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>1</t>
@@ -5373,7 +5374,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504663</v>
+        <v>504725</v>
       </c>
       <c r="R41" t="n">
         <v>6611991</v>
@@ -5413,7 +5414,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5422,6 +5423,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5440,7 +5442,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553036</v>
+        <v>124553015</v>
       </c>
       <c r="B42" t="n">
         <v>105676</v>
@@ -5484,10 +5486,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504667</v>
+        <v>504740</v>
       </c>
       <c r="R42" t="n">
-        <v>6611981</v>
+        <v>6612008</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5524,7 +5526,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5551,7 +5553,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553000</v>
+        <v>124553032</v>
       </c>
       <c r="B43" t="n">
         <v>105676</v>
@@ -5586,7 +5588,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5595,13 +5597,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504774</v>
+        <v>504686</v>
       </c>
       <c r="R43" t="n">
-        <v>6611972</v>
+        <v>6611987</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5635,7 +5637,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5662,7 +5664,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553017</v>
+        <v>124553038</v>
       </c>
       <c r="B44" t="n">
         <v>105676</v>
@@ -5706,10 +5708,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504749</v>
+        <v>504663</v>
       </c>
       <c r="R44" t="n">
-        <v>6612014</v>
+        <v>6611991</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5746,7 +5748,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5773,7 +5775,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553016</v>
+        <v>124553003</v>
       </c>
       <c r="B45" t="n">
         <v>105676</v>
@@ -5808,7 +5810,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5817,10 +5819,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504741</v>
+        <v>504753</v>
       </c>
       <c r="R45" t="n">
-        <v>6612008</v>
+        <v>6611982</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5857,7 +5859,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5884,7 +5886,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553005</v>
+        <v>124553013</v>
       </c>
       <c r="B46" t="n">
         <v>105676</v>
@@ -5928,10 +5930,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504746</v>
+        <v>504727</v>
       </c>
       <c r="R46" t="n">
-        <v>6611972</v>
+        <v>6611975</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5968,7 +5970,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5995,10 +5997,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553011</v>
+        <v>124553010</v>
       </c>
       <c r="B47" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6007,20 +6009,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6039,10 +6041,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504726</v>
+        <v>504732</v>
       </c>
       <c r="R47" t="n">
-        <v>6611959</v>
+        <v>6611958</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6075,11 +6077,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6106,7 +6103,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553040</v>
+        <v>124553037</v>
       </c>
       <c r="B48" t="n">
         <v>105676</v>
@@ -6141,7 +6138,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6150,10 +6147,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504638</v>
+        <v>504667</v>
       </c>
       <c r="R48" t="n">
-        <v>6611981</v>
+        <v>6611989</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6190,7 +6187,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6217,7 +6214,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553012</v>
+        <v>124553031</v>
       </c>
       <c r="B49" t="n">
         <v>105676</v>
@@ -6252,7 +6249,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6261,10 +6258,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504726</v>
+        <v>504697</v>
       </c>
       <c r="R49" t="n">
-        <v>6611974</v>
+        <v>6612016</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6301,7 +6298,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6328,7 +6325,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553015</v>
+        <v>124553000</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6363,7 +6360,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6372,13 +6369,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504740</v>
+        <v>504774</v>
       </c>
       <c r="R50" t="n">
-        <v>6612008</v>
+        <v>6611972</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6412,7 +6409,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6439,7 +6436,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553004</v>
+        <v>124553043</v>
       </c>
       <c r="B51" t="n">
         <v>105676</v>
@@ -6474,7 +6471,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6483,10 +6480,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504750</v>
+        <v>504644</v>
       </c>
       <c r="R51" t="n">
-        <v>6611973</v>
+        <v>6611959</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6523,7 +6520,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6550,10 +6547,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553014</v>
+        <v>124553002</v>
       </c>
       <c r="B52" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6562,23 +6559,27 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>1</t>
@@ -6590,7 +6591,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504725</v>
+        <v>504759</v>
       </c>
       <c r="R52" t="n">
         <v>6611991</v>
@@ -6630,7 +6631,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6639,7 +6640,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6658,7 +6658,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553013</v>
+        <v>124553042</v>
       </c>
       <c r="B53" t="n">
         <v>105676</v>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504727</v>
+        <v>504630</v>
       </c>
       <c r="R53" t="n">
-        <v>6611975</v>
+        <v>6611972</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553033</v>
+        <v>124553012</v>
       </c>
       <c r="B54" t="n">
         <v>105676</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504688</v>
+        <v>504726</v>
       </c>
       <c r="R54" t="n">
-        <v>6611985</v>
+        <v>6611974</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553017</v>
+        <v>124553032</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504749</v>
+        <v>504686</v>
       </c>
       <c r="R29" t="n">
-        <v>6612014</v>
+        <v>6611987</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553033</v>
+        <v>124553000</v>
       </c>
       <c r="B30" t="n">
         <v>105676</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4157,13 +4157,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504688</v>
+        <v>504774</v>
       </c>
       <c r="R30" t="n">
-        <v>6611985</v>
+        <v>6611972</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4224,7 +4224,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553004</v>
+        <v>124553016</v>
       </c>
       <c r="B31" t="n">
         <v>105676</v>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504750</v>
+        <v>504741</v>
       </c>
       <c r="R31" t="n">
-        <v>6611973</v>
+        <v>6612008</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,7 +4335,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553011</v>
+        <v>124553040</v>
       </c>
       <c r="B32" t="n">
         <v>105676</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504726</v>
+        <v>504638</v>
       </c>
       <c r="R32" t="n">
-        <v>6611959</v>
+        <v>6611981</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,7 +4446,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553036</v>
+        <v>124553003</v>
       </c>
       <c r="B33" t="n">
         <v>105676</v>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504667</v>
+        <v>504753</v>
       </c>
       <c r="R33" t="n">
-        <v>6611981</v>
+        <v>6611982</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4557,7 +4557,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553035</v>
+        <v>124553005</v>
       </c>
       <c r="B34" t="n">
         <v>105676</v>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504665</v>
+        <v>504746</v>
       </c>
       <c r="R34" t="n">
-        <v>6611970</v>
+        <v>6611972</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4668,7 +4668,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553034</v>
+        <v>124553035</v>
       </c>
       <c r="B35" t="n">
         <v>105676</v>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504683</v>
+        <v>504665</v>
       </c>
       <c r="R35" t="n">
-        <v>6611983</v>
+        <v>6611970</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4779,7 +4779,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553016</v>
+        <v>124553012</v>
       </c>
       <c r="B36" t="n">
         <v>105676</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504741</v>
+        <v>504726</v>
       </c>
       <c r="R36" t="n">
-        <v>6612008</v>
+        <v>6611974</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4890,7 +4890,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553039</v>
+        <v>124553038</v>
       </c>
       <c r="B37" t="n">
         <v>105676</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504635</v>
+        <v>504663</v>
       </c>
       <c r="R37" t="n">
-        <v>6612001</v>
+        <v>6611991</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5001,7 +5001,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553005</v>
+        <v>124553036</v>
       </c>
       <c r="B38" t="n">
         <v>105676</v>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504746</v>
+        <v>504667</v>
       </c>
       <c r="R38" t="n">
-        <v>6611972</v>
+        <v>6611981</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5112,7 +5112,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553040</v>
+        <v>124553037</v>
       </c>
       <c r="B39" t="n">
         <v>105676</v>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504638</v>
+        <v>504667</v>
       </c>
       <c r="R39" t="n">
-        <v>6611981</v>
+        <v>6611989</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5223,7 +5223,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553030</v>
+        <v>124553002</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504720</v>
+        <v>504759</v>
       </c>
       <c r="R40" t="n">
-        <v>6612011</v>
+        <v>6611991</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5334,10 +5334,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553014</v>
+        <v>124553031</v>
       </c>
       <c r="B41" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5346,26 +5346,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5374,10 +5378,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504725</v>
+        <v>504697</v>
       </c>
       <c r="R41" t="n">
-        <v>6611991</v>
+        <v>6612016</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5414,7 +5418,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5423,7 +5427,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5442,7 +5445,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553015</v>
+        <v>124553004</v>
       </c>
       <c r="B42" t="n">
         <v>105676</v>
@@ -5486,10 +5489,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504740</v>
+        <v>504750</v>
       </c>
       <c r="R42" t="n">
-        <v>6612008</v>
+        <v>6611973</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5526,7 +5529,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5553,7 +5556,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553032</v>
+        <v>124553034</v>
       </c>
       <c r="B43" t="n">
         <v>105676</v>
@@ -5588,7 +5591,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5597,10 +5600,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504686</v>
+        <v>504683</v>
       </c>
       <c r="R43" t="n">
-        <v>6611987</v>
+        <v>6611983</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5637,7 +5640,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5664,7 +5667,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553038</v>
+        <v>124553043</v>
       </c>
       <c r="B44" t="n">
         <v>105676</v>
@@ -5699,7 +5702,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5708,10 +5711,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504663</v>
+        <v>504644</v>
       </c>
       <c r="R44" t="n">
-        <v>6611991</v>
+        <v>6611959</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5748,7 +5751,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5775,7 +5778,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553003</v>
+        <v>124553015</v>
       </c>
       <c r="B45" t="n">
         <v>105676</v>
@@ -5810,7 +5813,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5819,10 +5822,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504753</v>
+        <v>504740</v>
       </c>
       <c r="R45" t="n">
-        <v>6611982</v>
+        <v>6612008</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5859,7 +5862,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5886,7 +5889,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553013</v>
+        <v>124553039</v>
       </c>
       <c r="B46" t="n">
         <v>105676</v>
@@ -5921,7 +5924,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5930,10 +5933,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504727</v>
+        <v>504635</v>
       </c>
       <c r="R46" t="n">
-        <v>6611975</v>
+        <v>6612001</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5970,7 +5973,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5997,10 +6000,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553010</v>
+        <v>124553017</v>
       </c>
       <c r="B47" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6009,20 +6012,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6041,10 +6044,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504732</v>
+        <v>504749</v>
       </c>
       <c r="R47" t="n">
-        <v>6611958</v>
+        <v>6612014</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6077,6 +6080,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6103,7 +6111,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553037</v>
+        <v>124553042</v>
       </c>
       <c r="B48" t="n">
         <v>105676</v>
@@ -6138,7 +6146,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6147,10 +6155,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504667</v>
+        <v>504630</v>
       </c>
       <c r="R48" t="n">
-        <v>6611989</v>
+        <v>6611972</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6187,7 +6195,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6214,10 +6222,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553031</v>
+        <v>124553014</v>
       </c>
       <c r="B49" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6226,30 +6234,26 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6258,10 +6262,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504697</v>
+        <v>504725</v>
       </c>
       <c r="R49" t="n">
-        <v>6612016</v>
+        <v>6611991</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6298,7 +6302,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6307,6 +6311,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6325,7 +6330,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553000</v>
+        <v>124553013</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6360,7 +6365,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6369,13 +6374,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504774</v>
+        <v>504727</v>
       </c>
       <c r="R50" t="n">
-        <v>6611972</v>
+        <v>6611975</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6409,7 +6414,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6436,7 +6441,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553043</v>
+        <v>124553011</v>
       </c>
       <c r="B51" t="n">
         <v>105676</v>
@@ -6471,7 +6476,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6480,7 +6485,7 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504644</v>
+        <v>504726</v>
       </c>
       <c r="R51" t="n">
         <v>6611959</v>
@@ -6520,7 +6525,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6547,10 +6552,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553002</v>
+        <v>124553010</v>
       </c>
       <c r="B52" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6559,20 +6564,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6591,10 +6596,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504759</v>
+        <v>504732</v>
       </c>
       <c r="R52" t="n">
-        <v>6611991</v>
+        <v>6611958</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6627,11 +6632,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6658,7 +6658,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553042</v>
+        <v>124553033</v>
       </c>
       <c r="B53" t="n">
         <v>105676</v>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504630</v>
+        <v>504688</v>
       </c>
       <c r="R53" t="n">
-        <v>6611972</v>
+        <v>6611985</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553012</v>
+        <v>124553030</v>
       </c>
       <c r="B54" t="n">
         <v>105676</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504726</v>
+        <v>504720</v>
       </c>
       <c r="R54" t="n">
-        <v>6611974</v>
+        <v>6612011</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553032</v>
+        <v>124553043</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504686</v>
+        <v>504644</v>
       </c>
       <c r="R29" t="n">
-        <v>6611987</v>
+        <v>6611959</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553000</v>
+        <v>124553017</v>
       </c>
       <c r="B30" t="n">
         <v>105676</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4157,13 +4157,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504774</v>
+        <v>504749</v>
       </c>
       <c r="R30" t="n">
-        <v>6611972</v>
+        <v>6612014</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4224,7 +4224,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553016</v>
+        <v>124553033</v>
       </c>
       <c r="B31" t="n">
         <v>105676</v>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504741</v>
+        <v>504688</v>
       </c>
       <c r="R31" t="n">
-        <v>6612008</v>
+        <v>6611985</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,10 +4335,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553040</v>
+        <v>124553010</v>
       </c>
       <c r="B32" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4347,20 +4347,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504638</v>
+        <v>504732</v>
       </c>
       <c r="R32" t="n">
-        <v>6611981</v>
+        <v>6611958</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4415,11 +4415,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,7 +4441,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553003</v>
+        <v>124553004</v>
       </c>
       <c r="B33" t="n">
         <v>105676</v>
@@ -4481,7 +4476,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4490,10 +4485,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504753</v>
+        <v>504750</v>
       </c>
       <c r="R33" t="n">
-        <v>6611982</v>
+        <v>6611973</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4530,7 +4525,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4557,7 +4552,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553005</v>
+        <v>124553030</v>
       </c>
       <c r="B34" t="n">
         <v>105676</v>
@@ -4592,7 +4587,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4601,10 +4596,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504746</v>
+        <v>504720</v>
       </c>
       <c r="R34" t="n">
-        <v>6611972</v>
+        <v>6612011</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4641,7 +4636,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4668,7 +4663,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553035</v>
+        <v>124553003</v>
       </c>
       <c r="B35" t="n">
         <v>105676</v>
@@ -4703,7 +4698,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4712,10 +4707,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504665</v>
+        <v>504753</v>
       </c>
       <c r="R35" t="n">
-        <v>6611970</v>
+        <v>6611982</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4752,7 +4747,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4779,7 +4774,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553012</v>
+        <v>124553037</v>
       </c>
       <c r="B36" t="n">
         <v>105676</v>
@@ -4814,7 +4809,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4823,10 +4818,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504726</v>
+        <v>504667</v>
       </c>
       <c r="R36" t="n">
-        <v>6611974</v>
+        <v>6611989</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4863,7 +4858,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4890,7 +4885,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553038</v>
+        <v>124553031</v>
       </c>
       <c r="B37" t="n">
         <v>105676</v>
@@ -4925,7 +4920,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4934,10 +4929,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504663</v>
+        <v>504697</v>
       </c>
       <c r="R37" t="n">
-        <v>6611991</v>
+        <v>6612016</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4974,7 +4969,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5001,7 +4996,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553036</v>
+        <v>124553011</v>
       </c>
       <c r="B38" t="n">
         <v>105676</v>
@@ -5045,10 +5040,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504667</v>
+        <v>504726</v>
       </c>
       <c r="R38" t="n">
-        <v>6611981</v>
+        <v>6611959</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5085,7 +5080,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5112,10 +5107,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553037</v>
+        <v>124553014</v>
       </c>
       <c r="B39" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5124,30 +5119,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5156,10 +5147,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504667</v>
+        <v>504725</v>
       </c>
       <c r="R39" t="n">
-        <v>6611989</v>
+        <v>6611991</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5196,7 +5187,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5205,6 +5196,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5223,7 +5215,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553002</v>
+        <v>124553013</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5267,10 +5259,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504759</v>
+        <v>504727</v>
       </c>
       <c r="R40" t="n">
-        <v>6611991</v>
+        <v>6611975</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5307,7 +5299,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5334,7 +5326,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553031</v>
+        <v>124553042</v>
       </c>
       <c r="B41" t="n">
         <v>105676</v>
@@ -5369,7 +5361,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5378,10 +5370,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504697</v>
+        <v>504630</v>
       </c>
       <c r="R41" t="n">
-        <v>6612016</v>
+        <v>6611972</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5418,7 +5410,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5445,7 +5437,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553004</v>
+        <v>124553002</v>
       </c>
       <c r="B42" t="n">
         <v>105676</v>
@@ -5489,10 +5481,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504750</v>
+        <v>504759</v>
       </c>
       <c r="R42" t="n">
-        <v>6611973</v>
+        <v>6611991</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5529,7 +5521,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5556,7 +5548,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553034</v>
+        <v>124553016</v>
       </c>
       <c r="B43" t="n">
         <v>105676</v>
@@ -5591,7 +5583,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5600,10 +5592,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504683</v>
+        <v>504741</v>
       </c>
       <c r="R43" t="n">
-        <v>6611983</v>
+        <v>6612008</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5667,7 +5659,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553043</v>
+        <v>124553015</v>
       </c>
       <c r="B44" t="n">
         <v>105676</v>
@@ -5702,7 +5694,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5711,10 +5703,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504644</v>
+        <v>504740</v>
       </c>
       <c r="R44" t="n">
-        <v>6611959</v>
+        <v>6612008</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5751,7 +5743,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5778,7 +5770,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553015</v>
+        <v>124553035</v>
       </c>
       <c r="B45" t="n">
         <v>105676</v>
@@ -5822,10 +5814,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504740</v>
+        <v>504665</v>
       </c>
       <c r="R45" t="n">
-        <v>6612008</v>
+        <v>6611970</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5862,7 +5854,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5889,7 +5881,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553039</v>
+        <v>124553012</v>
       </c>
       <c r="B46" t="n">
         <v>105676</v>
@@ -5924,7 +5916,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5933,10 +5925,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504635</v>
+        <v>504726</v>
       </c>
       <c r="R46" t="n">
-        <v>6612001</v>
+        <v>6611974</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5973,7 +5965,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6000,7 +5992,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553017</v>
+        <v>124553036</v>
       </c>
       <c r="B47" t="n">
         <v>105676</v>
@@ -6044,10 +6036,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504749</v>
+        <v>504667</v>
       </c>
       <c r="R47" t="n">
-        <v>6612014</v>
+        <v>6611981</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6084,7 +6076,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6111,7 +6103,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553042</v>
+        <v>124553038</v>
       </c>
       <c r="B48" t="n">
         <v>105676</v>
@@ -6146,7 +6138,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6155,10 +6147,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504630</v>
+        <v>504663</v>
       </c>
       <c r="R48" t="n">
-        <v>6611972</v>
+        <v>6611991</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6195,7 +6187,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6222,10 +6214,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553014</v>
+        <v>124553000</v>
       </c>
       <c r="B49" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6234,26 +6226,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6262,13 +6258,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504725</v>
+        <v>504774</v>
       </c>
       <c r="R49" t="n">
-        <v>6611991</v>
+        <v>6611972</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6302,7 +6298,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6311,7 +6307,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6330,7 +6325,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553013</v>
+        <v>124553005</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6374,10 +6369,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504727</v>
+        <v>504746</v>
       </c>
       <c r="R50" t="n">
-        <v>6611975</v>
+        <v>6611972</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6414,7 +6409,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6441,7 +6436,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553011</v>
+        <v>124553032</v>
       </c>
       <c r="B51" t="n">
         <v>105676</v>
@@ -6476,7 +6471,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6485,10 +6480,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504726</v>
+        <v>504686</v>
       </c>
       <c r="R51" t="n">
-        <v>6611959</v>
+        <v>6611987</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6525,7 +6520,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6552,10 +6547,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553010</v>
+        <v>124553039</v>
       </c>
       <c r="B52" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6564,20 +6559,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6587,7 +6582,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6596,10 +6591,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504732</v>
+        <v>504635</v>
       </c>
       <c r="R52" t="n">
-        <v>6611958</v>
+        <v>6612001</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6632,6 +6627,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6658,7 +6658,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553033</v>
+        <v>124553040</v>
       </c>
       <c r="B53" t="n">
         <v>105676</v>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504688</v>
+        <v>504638</v>
       </c>
       <c r="R53" t="n">
-        <v>6611985</v>
+        <v>6611981</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553030</v>
+        <v>124553034</v>
       </c>
       <c r="B54" t="n">
         <v>105676</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504720</v>
+        <v>504683</v>
       </c>
       <c r="R54" t="n">
-        <v>6612011</v>
+        <v>6611983</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -5437,7 +5437,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553002</v>
+        <v>124553016</v>
       </c>
       <c r="B42" t="n">
         <v>105676</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504759</v>
+        <v>504741</v>
       </c>
       <c r="R42" t="n">
-        <v>6611991</v>
+        <v>6612008</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5548,7 +5548,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553016</v>
+        <v>124553002</v>
       </c>
       <c r="B43" t="n">
         <v>105676</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504741</v>
+        <v>504759</v>
       </c>
       <c r="R43" t="n">
-        <v>6612008</v>
+        <v>6611991</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553043</v>
+        <v>124553017</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504644</v>
+        <v>504749</v>
       </c>
       <c r="R29" t="n">
-        <v>6611959</v>
+        <v>6612014</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553017</v>
+        <v>124553013</v>
       </c>
       <c r="B30" t="n">
         <v>105676</v>
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504749</v>
+        <v>504727</v>
       </c>
       <c r="R30" t="n">
-        <v>6612014</v>
+        <v>6611975</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4224,7 +4224,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553033</v>
+        <v>124553015</v>
       </c>
       <c r="B31" t="n">
         <v>105676</v>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504688</v>
+        <v>504740</v>
       </c>
       <c r="R31" t="n">
-        <v>6611985</v>
+        <v>6612008</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,10 +4335,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553010</v>
+        <v>124553039</v>
       </c>
       <c r="B32" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4347,20 +4347,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504732</v>
+        <v>504635</v>
       </c>
       <c r="R32" t="n">
-        <v>6611958</v>
+        <v>6612001</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4415,6 +4415,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4441,7 +4446,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553004</v>
+        <v>124553005</v>
       </c>
       <c r="B33" t="n">
         <v>105676</v>
@@ -4485,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504750</v>
+        <v>504746</v>
       </c>
       <c r="R33" t="n">
-        <v>6611973</v>
+        <v>6611972</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4525,7 +4530,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4552,7 +4557,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553030</v>
+        <v>124553040</v>
       </c>
       <c r="B34" t="n">
         <v>105676</v>
@@ -4596,10 +4601,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504720</v>
+        <v>504638</v>
       </c>
       <c r="R34" t="n">
-        <v>6612011</v>
+        <v>6611981</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4636,7 +4641,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4663,7 +4668,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553003</v>
+        <v>124553043</v>
       </c>
       <c r="B35" t="n">
         <v>105676</v>
@@ -4698,7 +4703,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4707,10 +4712,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504753</v>
+        <v>504644</v>
       </c>
       <c r="R35" t="n">
-        <v>6611982</v>
+        <v>6611959</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4747,7 +4752,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4774,7 +4779,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553037</v>
+        <v>124553032</v>
       </c>
       <c r="B36" t="n">
         <v>105676</v>
@@ -4809,7 +4814,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4818,10 +4823,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504667</v>
+        <v>504686</v>
       </c>
       <c r="R36" t="n">
-        <v>6611989</v>
+        <v>6611987</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4858,7 +4863,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4885,10 +4890,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553031</v>
+        <v>124553014</v>
       </c>
       <c r="B37" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4897,30 +4902,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4929,10 +4930,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504697</v>
+        <v>504725</v>
       </c>
       <c r="R37" t="n">
-        <v>6612016</v>
+        <v>6611991</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4969,7 +4970,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4978,6 +4979,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4996,7 +4998,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553011</v>
+        <v>124553037</v>
       </c>
       <c r="B38" t="n">
         <v>105676</v>
@@ -5031,7 +5033,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5040,10 +5042,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504726</v>
+        <v>504667</v>
       </c>
       <c r="R38" t="n">
-        <v>6611959</v>
+        <v>6611989</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5080,7 +5082,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5107,10 +5109,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553014</v>
+        <v>124553042</v>
       </c>
       <c r="B39" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5119,26 +5121,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5147,10 +5153,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504725</v>
+        <v>504630</v>
       </c>
       <c r="R39" t="n">
-        <v>6611991</v>
+        <v>6611972</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5187,7 +5193,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5196,7 +5202,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5215,7 +5220,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553013</v>
+        <v>124553002</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5259,10 +5264,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504727</v>
+        <v>504759</v>
       </c>
       <c r="R40" t="n">
-        <v>6611975</v>
+        <v>6611991</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5299,7 +5304,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5326,7 +5331,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553042</v>
+        <v>124553033</v>
       </c>
       <c r="B41" t="n">
         <v>105676</v>
@@ -5361,7 +5366,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5370,10 +5375,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504630</v>
+        <v>504688</v>
       </c>
       <c r="R41" t="n">
-        <v>6611972</v>
+        <v>6611985</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5410,7 +5415,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5548,7 +5553,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553002</v>
+        <v>124553000</v>
       </c>
       <c r="B43" t="n">
         <v>105676</v>
@@ -5583,7 +5588,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5592,13 +5597,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504759</v>
+        <v>504774</v>
       </c>
       <c r="R43" t="n">
-        <v>6611991</v>
+        <v>6611972</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5632,7 +5637,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5659,7 +5664,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553015</v>
+        <v>124553030</v>
       </c>
       <c r="B44" t="n">
         <v>105676</v>
@@ -5694,7 +5699,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5703,10 +5708,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504740</v>
+        <v>504720</v>
       </c>
       <c r="R44" t="n">
-        <v>6612008</v>
+        <v>6612011</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5743,7 +5748,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5770,7 +5775,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553035</v>
+        <v>124553003</v>
       </c>
       <c r="B45" t="n">
         <v>105676</v>
@@ -5805,7 +5810,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5814,10 +5819,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504665</v>
+        <v>504753</v>
       </c>
       <c r="R45" t="n">
-        <v>6611970</v>
+        <v>6611982</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5854,7 +5859,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5881,7 +5886,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553012</v>
+        <v>124553038</v>
       </c>
       <c r="B46" t="n">
         <v>105676</v>
@@ -5925,10 +5930,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504726</v>
+        <v>504663</v>
       </c>
       <c r="R46" t="n">
-        <v>6611974</v>
+        <v>6611991</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5965,7 +5970,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5992,7 +5997,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553036</v>
+        <v>124553011</v>
       </c>
       <c r="B47" t="n">
         <v>105676</v>
@@ -6036,10 +6041,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504667</v>
+        <v>504726</v>
       </c>
       <c r="R47" t="n">
-        <v>6611981</v>
+        <v>6611959</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6076,7 +6081,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6103,7 +6108,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553038</v>
+        <v>124553036</v>
       </c>
       <c r="B48" t="n">
         <v>105676</v>
@@ -6147,10 +6152,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504663</v>
+        <v>504667</v>
       </c>
       <c r="R48" t="n">
-        <v>6611991</v>
+        <v>6611981</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6187,7 +6192,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6214,10 +6219,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553000</v>
+        <v>124553010</v>
       </c>
       <c r="B49" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6226,20 +6231,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6249,7 +6254,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6258,13 +6263,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504774</v>
+        <v>504732</v>
       </c>
       <c r="R49" t="n">
-        <v>6611972</v>
+        <v>6611958</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6294,11 +6299,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6325,7 +6325,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553005</v>
+        <v>124553034</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504746</v>
+        <v>504683</v>
       </c>
       <c r="R50" t="n">
-        <v>6611972</v>
+        <v>6611983</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6436,7 +6436,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553032</v>
+        <v>124553012</v>
       </c>
       <c r="B51" t="n">
         <v>105676</v>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504686</v>
+        <v>504726</v>
       </c>
       <c r="R51" t="n">
-        <v>6611987</v>
+        <v>6611974</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6547,7 +6547,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553039</v>
+        <v>124553035</v>
       </c>
       <c r="B52" t="n">
         <v>105676</v>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504635</v>
+        <v>504665</v>
       </c>
       <c r="R52" t="n">
-        <v>6612001</v>
+        <v>6611970</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6658,7 +6658,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553040</v>
+        <v>124553031</v>
       </c>
       <c r="B53" t="n">
         <v>105676</v>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504638</v>
+        <v>504697</v>
       </c>
       <c r="R53" t="n">
-        <v>6611981</v>
+        <v>6612016</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553034</v>
+        <v>124553004</v>
       </c>
       <c r="B54" t="n">
         <v>105676</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504683</v>
+        <v>504750</v>
       </c>
       <c r="R54" t="n">
-        <v>6611983</v>
+        <v>6611973</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553017</v>
+        <v>124553033</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504749</v>
+        <v>504688</v>
       </c>
       <c r="R29" t="n">
-        <v>6612014</v>
+        <v>6611985</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553013</v>
+        <v>124553043</v>
       </c>
       <c r="B30" t="n">
         <v>105676</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504727</v>
+        <v>504644</v>
       </c>
       <c r="R30" t="n">
-        <v>6611975</v>
+        <v>6611959</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4224,7 +4224,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553015</v>
+        <v>124553042</v>
       </c>
       <c r="B31" t="n">
         <v>105676</v>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504740</v>
+        <v>504630</v>
       </c>
       <c r="R31" t="n">
-        <v>6612008</v>
+        <v>6611972</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,7 +4335,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553039</v>
+        <v>124553005</v>
       </c>
       <c r="B32" t="n">
         <v>105676</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504635</v>
+        <v>504746</v>
       </c>
       <c r="R32" t="n">
-        <v>6612001</v>
+        <v>6611972</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,10 +4446,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553005</v>
+        <v>124553014</v>
       </c>
       <c r="B33" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4458,27 +4458,23 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>1</t>
@@ -4490,10 +4486,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504746</v>
+        <v>504725</v>
       </c>
       <c r="R33" t="n">
-        <v>6611972</v>
+        <v>6611991</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4530,7 +4526,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4539,6 +4535,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4557,7 +4554,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553040</v>
+        <v>124553011</v>
       </c>
       <c r="B34" t="n">
         <v>105676</v>
@@ -4592,7 +4589,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4601,10 +4598,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504638</v>
+        <v>504726</v>
       </c>
       <c r="R34" t="n">
-        <v>6611981</v>
+        <v>6611959</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4641,7 +4638,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4668,7 +4665,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553043</v>
+        <v>124553000</v>
       </c>
       <c r="B35" t="n">
         <v>105676</v>
@@ -4703,7 +4700,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4712,13 +4709,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504644</v>
+        <v>504774</v>
       </c>
       <c r="R35" t="n">
-        <v>6611959</v>
+        <v>6611972</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4752,7 +4749,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4779,7 +4776,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553032</v>
+        <v>124553030</v>
       </c>
       <c r="B36" t="n">
         <v>105676</v>
@@ -4823,10 +4820,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504686</v>
+        <v>504720</v>
       </c>
       <c r="R36" t="n">
-        <v>6611987</v>
+        <v>6612011</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4863,7 +4860,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4890,10 +4887,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553014</v>
+        <v>124553039</v>
       </c>
       <c r="B37" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4902,26 +4899,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4930,10 +4931,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504725</v>
+        <v>504635</v>
       </c>
       <c r="R37" t="n">
-        <v>6611991</v>
+        <v>6612001</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4970,7 +4971,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4979,7 +4980,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4998,7 +4998,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553037</v>
+        <v>124553016</v>
       </c>
       <c r="B38" t="n">
         <v>105676</v>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504667</v>
+        <v>504741</v>
       </c>
       <c r="R38" t="n">
-        <v>6611989</v>
+        <v>6612008</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5109,7 +5109,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553042</v>
+        <v>124553015</v>
       </c>
       <c r="B39" t="n">
         <v>105676</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504630</v>
+        <v>504740</v>
       </c>
       <c r="R39" t="n">
-        <v>6611972</v>
+        <v>6612008</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5220,7 +5220,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553002</v>
+        <v>124553017</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504759</v>
+        <v>504749</v>
       </c>
       <c r="R40" t="n">
-        <v>6611991</v>
+        <v>6612014</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5331,7 +5331,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553033</v>
+        <v>124553035</v>
       </c>
       <c r="B41" t="n">
         <v>105676</v>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5375,10 +5375,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504688</v>
+        <v>504665</v>
       </c>
       <c r="R41" t="n">
-        <v>6611985</v>
+        <v>6611970</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5442,7 +5442,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553016</v>
+        <v>124553003</v>
       </c>
       <c r="B42" t="n">
         <v>105676</v>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5486,10 +5486,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504741</v>
+        <v>504753</v>
       </c>
       <c r="R42" t="n">
-        <v>6612008</v>
+        <v>6611982</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5553,7 +5553,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553000</v>
+        <v>124553002</v>
       </c>
       <c r="B43" t="n">
         <v>105676</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5597,13 +5597,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504774</v>
+        <v>504759</v>
       </c>
       <c r="R43" t="n">
-        <v>6611972</v>
+        <v>6611991</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5664,7 +5664,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553030</v>
+        <v>124553036</v>
       </c>
       <c r="B44" t="n">
         <v>105676</v>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5708,10 +5708,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504720</v>
+        <v>504667</v>
       </c>
       <c r="R44" t="n">
-        <v>6612011</v>
+        <v>6611981</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5775,7 +5775,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553003</v>
+        <v>124553012</v>
       </c>
       <c r="B45" t="n">
         <v>105676</v>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5819,10 +5819,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504753</v>
+        <v>504726</v>
       </c>
       <c r="R45" t="n">
-        <v>6611982</v>
+        <v>6611974</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5886,7 +5886,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553038</v>
+        <v>124553032</v>
       </c>
       <c r="B46" t="n">
         <v>105676</v>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504663</v>
+        <v>504686</v>
       </c>
       <c r="R46" t="n">
-        <v>6611991</v>
+        <v>6611987</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5997,7 +5997,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553011</v>
+        <v>124553038</v>
       </c>
       <c r="B47" t="n">
         <v>105676</v>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504726</v>
+        <v>504663</v>
       </c>
       <c r="R47" t="n">
-        <v>6611959</v>
+        <v>6611991</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6108,7 +6108,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553036</v>
+        <v>124553031</v>
       </c>
       <c r="B48" t="n">
         <v>105676</v>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6152,10 +6152,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504667</v>
+        <v>504697</v>
       </c>
       <c r="R48" t="n">
-        <v>6611981</v>
+        <v>6612016</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6219,10 +6219,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553010</v>
+        <v>124553013</v>
       </c>
       <c r="B49" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6231,20 +6231,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504732</v>
+        <v>504727</v>
       </c>
       <c r="R49" t="n">
-        <v>6611958</v>
+        <v>6611975</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6299,6 +6299,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6325,7 +6330,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553034</v>
+        <v>124553037</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6360,7 +6365,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6369,10 +6374,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504683</v>
+        <v>504667</v>
       </c>
       <c r="R50" t="n">
-        <v>6611983</v>
+        <v>6611989</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6409,7 +6414,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6436,10 +6441,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553012</v>
+        <v>124553010</v>
       </c>
       <c r="B51" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6448,20 +6453,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6480,10 +6485,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504726</v>
+        <v>504732</v>
       </c>
       <c r="R51" t="n">
-        <v>6611974</v>
+        <v>6611958</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6516,11 +6521,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6547,7 +6547,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553035</v>
+        <v>124553004</v>
       </c>
       <c r="B52" t="n">
         <v>105676</v>
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504665</v>
+        <v>504750</v>
       </c>
       <c r="R52" t="n">
-        <v>6611970</v>
+        <v>6611973</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6658,7 +6658,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553031</v>
+        <v>124553040</v>
       </c>
       <c r="B53" t="n">
         <v>105676</v>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504697</v>
+        <v>504638</v>
       </c>
       <c r="R53" t="n">
-        <v>6612016</v>
+        <v>6611981</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553004</v>
+        <v>124553034</v>
       </c>
       <c r="B54" t="n">
         <v>105676</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504750</v>
+        <v>504683</v>
       </c>
       <c r="R54" t="n">
-        <v>6611973</v>
+        <v>6611983</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553033</v>
+        <v>124553037</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504688</v>
+        <v>504667</v>
       </c>
       <c r="R29" t="n">
-        <v>6611985</v>
+        <v>6611989</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,10 +4113,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553043</v>
+        <v>124553010</v>
       </c>
       <c r="B30" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4125,20 +4125,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504644</v>
+        <v>504732</v>
       </c>
       <c r="R30" t="n">
-        <v>6611959</v>
+        <v>6611958</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4193,11 +4193,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4224,10 +4219,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553042</v>
+        <v>124553014</v>
       </c>
       <c r="B31" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4236,30 +4231,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4268,10 +4259,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504630</v>
+        <v>504725</v>
       </c>
       <c r="R31" t="n">
-        <v>6611972</v>
+        <v>6611991</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4308,7 +4299,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4317,6 +4308,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4335,7 +4327,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553005</v>
+        <v>124553036</v>
       </c>
       <c r="B32" t="n">
         <v>105676</v>
@@ -4379,10 +4371,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504746</v>
+        <v>504667</v>
       </c>
       <c r="R32" t="n">
-        <v>6611972</v>
+        <v>6611981</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4419,7 +4411,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,10 +4438,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553014</v>
+        <v>124553032</v>
       </c>
       <c r="B33" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4458,26 +4450,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4486,10 +4482,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504725</v>
+        <v>504686</v>
       </c>
       <c r="R33" t="n">
-        <v>6611991</v>
+        <v>6611987</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4526,7 +4522,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4535,7 +4531,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4554,7 +4549,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553011</v>
+        <v>124553005</v>
       </c>
       <c r="B34" t="n">
         <v>105676</v>
@@ -4598,10 +4593,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504726</v>
+        <v>504746</v>
       </c>
       <c r="R34" t="n">
-        <v>6611959</v>
+        <v>6611972</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4638,7 +4633,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4665,7 +4660,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553000</v>
+        <v>124553033</v>
       </c>
       <c r="B35" t="n">
         <v>105676</v>
@@ -4700,7 +4695,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4709,13 +4704,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504774</v>
+        <v>504688</v>
       </c>
       <c r="R35" t="n">
-        <v>6611972</v>
+        <v>6611985</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4749,7 +4744,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4776,7 +4771,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553030</v>
+        <v>124553043</v>
       </c>
       <c r="B36" t="n">
         <v>105676</v>
@@ -4811,7 +4806,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4820,10 +4815,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504720</v>
+        <v>504644</v>
       </c>
       <c r="R36" t="n">
-        <v>6612011</v>
+        <v>6611959</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4860,7 +4855,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4887,7 +4882,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553039</v>
+        <v>124553012</v>
       </c>
       <c r="B37" t="n">
         <v>105676</v>
@@ -4922,7 +4917,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4931,10 +4926,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504635</v>
+        <v>504726</v>
       </c>
       <c r="R37" t="n">
-        <v>6612001</v>
+        <v>6611974</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4971,7 +4966,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4998,7 +4993,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553016</v>
+        <v>124553038</v>
       </c>
       <c r="B38" t="n">
         <v>105676</v>
@@ -5033,7 +5028,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5042,10 +5037,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504741</v>
+        <v>504663</v>
       </c>
       <c r="R38" t="n">
-        <v>6612008</v>
+        <v>6611991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5082,7 +5077,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5109,7 +5104,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553015</v>
+        <v>124553013</v>
       </c>
       <c r="B39" t="n">
         <v>105676</v>
@@ -5153,10 +5148,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504740</v>
+        <v>504727</v>
       </c>
       <c r="R39" t="n">
-        <v>6612008</v>
+        <v>6611975</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5193,7 +5188,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5220,7 +5215,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553017</v>
+        <v>124553015</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5264,10 +5259,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504749</v>
+        <v>504740</v>
       </c>
       <c r="R40" t="n">
-        <v>6612014</v>
+        <v>6612008</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5304,7 +5299,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5331,7 +5326,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553035</v>
+        <v>124553042</v>
       </c>
       <c r="B41" t="n">
         <v>105676</v>
@@ -5366,7 +5361,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5375,10 +5370,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504665</v>
+        <v>504630</v>
       </c>
       <c r="R41" t="n">
-        <v>6611970</v>
+        <v>6611972</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5415,7 +5410,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5442,7 +5437,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553003</v>
+        <v>124553030</v>
       </c>
       <c r="B42" t="n">
         <v>105676</v>
@@ -5477,7 +5472,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5486,10 +5481,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504753</v>
+        <v>504720</v>
       </c>
       <c r="R42" t="n">
-        <v>6611982</v>
+        <v>6612011</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5553,7 +5548,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553002</v>
+        <v>124553004</v>
       </c>
       <c r="B43" t="n">
         <v>105676</v>
@@ -5597,10 +5592,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504759</v>
+        <v>504750</v>
       </c>
       <c r="R43" t="n">
-        <v>6611991</v>
+        <v>6611973</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5637,7 +5632,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5664,7 +5659,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553036</v>
+        <v>124553017</v>
       </c>
       <c r="B44" t="n">
         <v>105676</v>
@@ -5708,10 +5703,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504667</v>
+        <v>504749</v>
       </c>
       <c r="R44" t="n">
-        <v>6611981</v>
+        <v>6612014</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5748,7 +5743,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5775,7 +5770,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553012</v>
+        <v>124553034</v>
       </c>
       <c r="B45" t="n">
         <v>105676</v>
@@ -5810,7 +5805,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5819,10 +5814,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504726</v>
+        <v>504683</v>
       </c>
       <c r="R45" t="n">
-        <v>6611974</v>
+        <v>6611983</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5859,7 +5854,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5886,7 +5881,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553032</v>
+        <v>124553003</v>
       </c>
       <c r="B46" t="n">
         <v>105676</v>
@@ -5921,7 +5916,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5930,10 +5925,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504686</v>
+        <v>504753</v>
       </c>
       <c r="R46" t="n">
-        <v>6611987</v>
+        <v>6611982</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5970,7 +5965,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5997,7 +5992,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553038</v>
+        <v>124553039</v>
       </c>
       <c r="B47" t="n">
         <v>105676</v>
@@ -6032,7 +6027,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6041,10 +6036,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504663</v>
+        <v>504635</v>
       </c>
       <c r="R47" t="n">
-        <v>6611991</v>
+        <v>6612001</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6081,7 +6076,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6108,7 +6103,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553031</v>
+        <v>124553040</v>
       </c>
       <c r="B48" t="n">
         <v>105676</v>
@@ -6143,7 +6138,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6152,10 +6147,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504697</v>
+        <v>504638</v>
       </c>
       <c r="R48" t="n">
-        <v>6612016</v>
+        <v>6611981</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6192,7 +6187,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6219,7 +6214,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553013</v>
+        <v>124553000</v>
       </c>
       <c r="B49" t="n">
         <v>105676</v>
@@ -6254,7 +6249,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6263,13 +6258,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504727</v>
+        <v>504774</v>
       </c>
       <c r="R49" t="n">
-        <v>6611975</v>
+        <v>6611972</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6303,7 +6298,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6330,7 +6325,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553037</v>
+        <v>124553002</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6365,7 +6360,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6374,10 +6369,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504667</v>
+        <v>504759</v>
       </c>
       <c r="R50" t="n">
-        <v>6611989</v>
+        <v>6611991</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6414,7 +6409,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6441,10 +6436,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553010</v>
+        <v>124553011</v>
       </c>
       <c r="B51" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6453,20 +6448,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6485,10 +6480,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504732</v>
+        <v>504726</v>
       </c>
       <c r="R51" t="n">
-        <v>6611958</v>
+        <v>6611959</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6521,6 +6516,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6547,7 +6547,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553004</v>
+        <v>124553035</v>
       </c>
       <c r="B52" t="n">
         <v>105676</v>
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504750</v>
+        <v>504665</v>
       </c>
       <c r="R52" t="n">
-        <v>6611973</v>
+        <v>6611970</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6658,7 +6658,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553040</v>
+        <v>124553016</v>
       </c>
       <c r="B53" t="n">
         <v>105676</v>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504638</v>
+        <v>504741</v>
       </c>
       <c r="R53" t="n">
-        <v>6611981</v>
+        <v>6612008</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553034</v>
+        <v>124553031</v>
       </c>
       <c r="B54" t="n">
         <v>105676</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504683</v>
+        <v>504697</v>
       </c>
       <c r="R54" t="n">
-        <v>6611983</v>
+        <v>6612016</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4113,10 +4113,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553010</v>
+        <v>124553014</v>
       </c>
       <c r="B30" t="n">
-        <v>103528</v>
+        <v>102327</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4125,27 +4125,23 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222412</v>
+        <v>225046</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>1</t>
@@ -4157,10 +4153,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504732</v>
+        <v>504725</v>
       </c>
       <c r="R30" t="n">
-        <v>6611958</v>
+        <v>6611991</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4195,12 +4191,18 @@
           <t>2023-11-29</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4219,10 +4221,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553014</v>
+        <v>124553010</v>
       </c>
       <c r="B31" t="n">
-        <v>102327</v>
+        <v>103528</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4231,23 +4233,27 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>225046</v>
+        <v>222412</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>1</t>
@@ -4259,10 +4265,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504725</v>
+        <v>504732</v>
       </c>
       <c r="R31" t="n">
-        <v>6611991</v>
+        <v>6611958</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4297,18 +4303,12 @@
           <t>2023-11-29</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553037</v>
+        <v>124553035</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504667</v>
+        <v>504665</v>
       </c>
       <c r="R29" t="n">
-        <v>6611989</v>
+        <v>6611970</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,10 +4113,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553014</v>
+        <v>124553042</v>
       </c>
       <c r="B30" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4125,26 +4125,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4153,10 +4157,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504725</v>
+        <v>504630</v>
       </c>
       <c r="R30" t="n">
-        <v>6611991</v>
+        <v>6611972</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4193,7 +4197,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4202,7 +4206,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4221,10 +4224,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553010</v>
+        <v>124553036</v>
       </c>
       <c r="B31" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4233,20 +4236,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4265,10 +4268,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504732</v>
+        <v>504667</v>
       </c>
       <c r="R31" t="n">
-        <v>6611958</v>
+        <v>6611981</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4301,6 +4304,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4327,7 +4335,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553036</v>
+        <v>124553013</v>
       </c>
       <c r="B32" t="n">
         <v>105676</v>
@@ -4371,10 +4379,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504667</v>
+        <v>504727</v>
       </c>
       <c r="R32" t="n">
-        <v>6611981</v>
+        <v>6611975</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4411,7 +4419,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4438,7 +4446,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553032</v>
+        <v>124553037</v>
       </c>
       <c r="B33" t="n">
         <v>105676</v>
@@ -4473,7 +4481,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4482,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504686</v>
+        <v>504667</v>
       </c>
       <c r="R33" t="n">
-        <v>6611987</v>
+        <v>6611989</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4522,7 +4530,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4549,7 +4557,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553005</v>
+        <v>124553003</v>
       </c>
       <c r="B34" t="n">
         <v>105676</v>
@@ -4584,7 +4592,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4593,10 +4601,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504746</v>
+        <v>504753</v>
       </c>
       <c r="R34" t="n">
-        <v>6611972</v>
+        <v>6611982</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4633,7 +4641,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4660,7 +4668,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553033</v>
+        <v>124553015</v>
       </c>
       <c r="B35" t="n">
         <v>105676</v>
@@ -4695,7 +4703,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4704,10 +4712,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504688</v>
+        <v>504740</v>
       </c>
       <c r="R35" t="n">
-        <v>6611985</v>
+        <v>6612008</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4744,7 +4752,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4771,10 +4779,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553043</v>
+        <v>124553010</v>
       </c>
       <c r="B36" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4783,20 +4791,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4806,7 +4814,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4815,10 +4823,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504644</v>
+        <v>504732</v>
       </c>
       <c r="R36" t="n">
-        <v>6611959</v>
+        <v>6611958</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4851,11 +4859,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4882,7 +4885,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553012</v>
+        <v>124553011</v>
       </c>
       <c r="B37" t="n">
         <v>105676</v>
@@ -4929,7 +4932,7 @@
         <v>504726</v>
       </c>
       <c r="R37" t="n">
-        <v>6611974</v>
+        <v>6611959</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4966,7 +4969,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4993,7 +4996,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553038</v>
+        <v>124553030</v>
       </c>
       <c r="B38" t="n">
         <v>105676</v>
@@ -5028,7 +5031,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5037,10 +5040,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504663</v>
+        <v>504720</v>
       </c>
       <c r="R38" t="n">
-        <v>6611991</v>
+        <v>6612011</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5077,7 +5080,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5104,7 +5107,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553013</v>
+        <v>124553038</v>
       </c>
       <c r="B39" t="n">
         <v>105676</v>
@@ -5148,10 +5151,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504727</v>
+        <v>504663</v>
       </c>
       <c r="R39" t="n">
-        <v>6611975</v>
+        <v>6611991</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5188,7 +5191,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5215,7 +5218,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553015</v>
+        <v>124553040</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5250,7 +5253,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5259,10 +5262,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504740</v>
+        <v>504638</v>
       </c>
       <c r="R40" t="n">
-        <v>6612008</v>
+        <v>6611981</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5299,7 +5302,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5326,7 +5329,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553042</v>
+        <v>124553033</v>
       </c>
       <c r="B41" t="n">
         <v>105676</v>
@@ -5361,7 +5364,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5370,10 +5373,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504630</v>
+        <v>504688</v>
       </c>
       <c r="R41" t="n">
-        <v>6611972</v>
+        <v>6611985</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5410,7 +5413,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5437,10 +5440,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553030</v>
+        <v>124553014</v>
       </c>
       <c r="B42" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5449,30 +5452,26 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5481,10 +5480,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504720</v>
+        <v>504725</v>
       </c>
       <c r="R42" t="n">
-        <v>6612011</v>
+        <v>6611991</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5521,7 +5520,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5530,6 +5529,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5548,7 +5548,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553004</v>
+        <v>124553002</v>
       </c>
       <c r="B43" t="n">
         <v>105676</v>
@@ -5592,10 +5592,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504750</v>
+        <v>504759</v>
       </c>
       <c r="R43" t="n">
-        <v>6611973</v>
+        <v>6611991</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5659,7 +5659,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553017</v>
+        <v>124553031</v>
       </c>
       <c r="B44" t="n">
         <v>105676</v>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5703,10 +5703,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504749</v>
+        <v>504697</v>
       </c>
       <c r="R44" t="n">
-        <v>6612014</v>
+        <v>6612016</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5770,7 +5770,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553034</v>
+        <v>124553000</v>
       </c>
       <c r="B45" t="n">
         <v>105676</v>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5814,13 +5814,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504683</v>
+        <v>504774</v>
       </c>
       <c r="R45" t="n">
-        <v>6611983</v>
+        <v>6611972</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5881,7 +5881,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553003</v>
+        <v>124553012</v>
       </c>
       <c r="B46" t="n">
         <v>105676</v>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5925,10 +5925,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504753</v>
+        <v>504726</v>
       </c>
       <c r="R46" t="n">
-        <v>6611982</v>
+        <v>6611974</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5992,7 +5992,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553039</v>
+        <v>124553034</v>
       </c>
       <c r="B47" t="n">
         <v>105676</v>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504635</v>
+        <v>504683</v>
       </c>
       <c r="R47" t="n">
-        <v>6612001</v>
+        <v>6611983</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6103,7 +6103,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553040</v>
+        <v>124553032</v>
       </c>
       <c r="B48" t="n">
         <v>105676</v>
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504638</v>
+        <v>504686</v>
       </c>
       <c r="R48" t="n">
-        <v>6611981</v>
+        <v>6611987</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6214,7 +6214,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553000</v>
+        <v>124553039</v>
       </c>
       <c r="B49" t="n">
         <v>105676</v>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6258,13 +6258,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504774</v>
+        <v>504635</v>
       </c>
       <c r="R49" t="n">
-        <v>6611972</v>
+        <v>6612001</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6325,7 +6325,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553002</v>
+        <v>124553043</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504759</v>
+        <v>504644</v>
       </c>
       <c r="R50" t="n">
-        <v>6611991</v>
+        <v>6611959</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6436,7 +6436,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553011</v>
+        <v>124553004</v>
       </c>
       <c r="B51" t="n">
         <v>105676</v>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504726</v>
+        <v>504750</v>
       </c>
       <c r="R51" t="n">
-        <v>6611959</v>
+        <v>6611973</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6547,7 +6547,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553035</v>
+        <v>124553017</v>
       </c>
       <c r="B52" t="n">
         <v>105676</v>
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504665</v>
+        <v>504749</v>
       </c>
       <c r="R52" t="n">
-        <v>6611970</v>
+        <v>6612014</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553031</v>
+        <v>124553005</v>
       </c>
       <c r="B54" t="n">
         <v>105676</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504697</v>
+        <v>504746</v>
       </c>
       <c r="R54" t="n">
-        <v>6612016</v>
+        <v>6611972</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553035</v>
+        <v>124553030</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504665</v>
+        <v>504720</v>
       </c>
       <c r="R29" t="n">
-        <v>6611970</v>
+        <v>6612011</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553042</v>
+        <v>124553013</v>
       </c>
       <c r="B30" t="n">
         <v>105676</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504630</v>
+        <v>504727</v>
       </c>
       <c r="R30" t="n">
-        <v>6611972</v>
+        <v>6611975</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4224,7 +4224,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553036</v>
+        <v>124553005</v>
       </c>
       <c r="B31" t="n">
         <v>105676</v>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504667</v>
+        <v>504746</v>
       </c>
       <c r="R31" t="n">
-        <v>6611981</v>
+        <v>6611972</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,7 +4335,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553013</v>
+        <v>124553000</v>
       </c>
       <c r="B32" t="n">
         <v>105676</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4379,13 +4379,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504727</v>
+        <v>504774</v>
       </c>
       <c r="R32" t="n">
-        <v>6611975</v>
+        <v>6611972</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,7 +4446,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553037</v>
+        <v>124553016</v>
       </c>
       <c r="B33" t="n">
         <v>105676</v>
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504667</v>
+        <v>504741</v>
       </c>
       <c r="R33" t="n">
-        <v>6611989</v>
+        <v>6612008</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4557,7 +4557,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553003</v>
+        <v>124553035</v>
       </c>
       <c r="B34" t="n">
         <v>105676</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504753</v>
+        <v>504665</v>
       </c>
       <c r="R34" t="n">
-        <v>6611982</v>
+        <v>6611970</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4668,7 +4668,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553015</v>
+        <v>124553012</v>
       </c>
       <c r="B35" t="n">
         <v>105676</v>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504740</v>
+        <v>504726</v>
       </c>
       <c r="R35" t="n">
-        <v>6612008</v>
+        <v>6611974</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4779,10 +4779,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553010</v>
+        <v>124553011</v>
       </c>
       <c r="B36" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4791,20 +4791,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504732</v>
+        <v>504726</v>
       </c>
       <c r="R36" t="n">
-        <v>6611958</v>
+        <v>6611959</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4859,6 +4859,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4885,7 +4890,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553011</v>
+        <v>124553004</v>
       </c>
       <c r="B37" t="n">
         <v>105676</v>
@@ -4929,10 +4934,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504726</v>
+        <v>504750</v>
       </c>
       <c r="R37" t="n">
-        <v>6611959</v>
+        <v>6611973</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4969,7 +4974,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4996,7 +5001,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553030</v>
+        <v>124553042</v>
       </c>
       <c r="B38" t="n">
         <v>105676</v>
@@ -5031,7 +5036,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5040,10 +5045,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504720</v>
+        <v>504630</v>
       </c>
       <c r="R38" t="n">
-        <v>6612011</v>
+        <v>6611972</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5080,7 +5085,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5107,10 +5112,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553038</v>
+        <v>124553014</v>
       </c>
       <c r="B39" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5119,27 +5124,23 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>1</t>
@@ -5151,7 +5152,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504663</v>
+        <v>504725</v>
       </c>
       <c r="R39" t="n">
         <v>6611991</v>
@@ -5191,7 +5192,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5200,6 +5201,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5218,7 +5220,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553040</v>
+        <v>124553015</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5253,7 +5255,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5262,10 +5264,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504638</v>
+        <v>504740</v>
       </c>
       <c r="R40" t="n">
-        <v>6611981</v>
+        <v>6612008</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5302,7 +5304,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5329,7 +5331,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553033</v>
+        <v>124553036</v>
       </c>
       <c r="B41" t="n">
         <v>105676</v>
@@ -5364,7 +5366,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5373,10 +5375,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504688</v>
+        <v>504667</v>
       </c>
       <c r="R41" t="n">
-        <v>6611985</v>
+        <v>6611981</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5413,7 +5415,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5440,10 +5442,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553014</v>
+        <v>124553032</v>
       </c>
       <c r="B42" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5452,26 +5454,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5480,10 +5486,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504725</v>
+        <v>504686</v>
       </c>
       <c r="R42" t="n">
-        <v>6611991</v>
+        <v>6611987</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5520,7 +5526,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5529,7 +5535,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5548,7 +5553,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553002</v>
+        <v>124553031</v>
       </c>
       <c r="B43" t="n">
         <v>105676</v>
@@ -5583,7 +5588,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5592,10 +5597,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504759</v>
+        <v>504697</v>
       </c>
       <c r="R43" t="n">
-        <v>6611991</v>
+        <v>6612016</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5632,7 +5637,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5659,7 +5664,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553031</v>
+        <v>124553017</v>
       </c>
       <c r="B44" t="n">
         <v>105676</v>
@@ -5694,7 +5699,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5703,10 +5708,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504697</v>
+        <v>504749</v>
       </c>
       <c r="R44" t="n">
-        <v>6612016</v>
+        <v>6612014</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5743,7 +5748,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5770,7 +5775,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553000</v>
+        <v>124553003</v>
       </c>
       <c r="B45" t="n">
         <v>105676</v>
@@ -5805,7 +5810,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5814,13 +5819,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504774</v>
+        <v>504753</v>
       </c>
       <c r="R45" t="n">
-        <v>6611972</v>
+        <v>6611982</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5854,7 +5859,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5881,7 +5886,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553012</v>
+        <v>124553037</v>
       </c>
       <c r="B46" t="n">
         <v>105676</v>
@@ -5916,7 +5921,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5925,10 +5930,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504726</v>
+        <v>504667</v>
       </c>
       <c r="R46" t="n">
-        <v>6611974</v>
+        <v>6611989</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5965,7 +5970,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5992,7 +5997,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553034</v>
+        <v>124553002</v>
       </c>
       <c r="B47" t="n">
         <v>105676</v>
@@ -6027,7 +6032,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6036,10 +6041,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504683</v>
+        <v>504759</v>
       </c>
       <c r="R47" t="n">
-        <v>6611983</v>
+        <v>6611991</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6076,7 +6081,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6103,10 +6108,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553032</v>
+        <v>124553010</v>
       </c>
       <c r="B48" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6115,20 +6120,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6138,7 +6143,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6147,10 +6152,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504686</v>
+        <v>504732</v>
       </c>
       <c r="R48" t="n">
-        <v>6611987</v>
+        <v>6611958</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6183,11 +6188,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6325,7 +6325,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553043</v>
+        <v>124553033</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504644</v>
+        <v>504688</v>
       </c>
       <c r="R50" t="n">
-        <v>6611959</v>
+        <v>6611985</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6436,7 +6436,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553004</v>
+        <v>124553038</v>
       </c>
       <c r="B51" t="n">
         <v>105676</v>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504750</v>
+        <v>504663</v>
       </c>
       <c r="R51" t="n">
-        <v>6611973</v>
+        <v>6611991</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6547,7 +6547,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553017</v>
+        <v>124553040</v>
       </c>
       <c r="B52" t="n">
         <v>105676</v>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504749</v>
+        <v>504638</v>
       </c>
       <c r="R52" t="n">
-        <v>6612014</v>
+        <v>6611981</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6658,7 +6658,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553016</v>
+        <v>124553034</v>
       </c>
       <c r="B53" t="n">
         <v>105676</v>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504741</v>
+        <v>504683</v>
       </c>
       <c r="R53" t="n">
-        <v>6612008</v>
+        <v>6611983</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6769,7 +6769,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553005</v>
+        <v>124553043</v>
       </c>
       <c r="B54" t="n">
         <v>105676</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504746</v>
+        <v>504644</v>
       </c>
       <c r="R54" t="n">
-        <v>6611972</v>
+        <v>6611959</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553030</v>
+        <v>124553017</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504720</v>
+        <v>504749</v>
       </c>
       <c r="R29" t="n">
-        <v>6612011</v>
+        <v>6612014</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553013</v>
+        <v>124553012</v>
       </c>
       <c r="B30" t="n">
         <v>105676</v>
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504727</v>
+        <v>504726</v>
       </c>
       <c r="R30" t="n">
-        <v>6611975</v>
+        <v>6611974</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4224,7 +4224,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553005</v>
+        <v>124553037</v>
       </c>
       <c r="B31" t="n">
         <v>105676</v>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504746</v>
+        <v>504667</v>
       </c>
       <c r="R31" t="n">
-        <v>6611972</v>
+        <v>6611989</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,7 +4335,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553000</v>
+        <v>124553031</v>
       </c>
       <c r="B32" t="n">
         <v>105676</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4379,13 +4379,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504774</v>
+        <v>504697</v>
       </c>
       <c r="R32" t="n">
-        <v>6611972</v>
+        <v>6612016</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,7 +4446,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553016</v>
+        <v>124553042</v>
       </c>
       <c r="B33" t="n">
         <v>105676</v>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504741</v>
+        <v>504630</v>
       </c>
       <c r="R33" t="n">
-        <v>6612008</v>
+        <v>6611972</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4668,7 +4668,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553012</v>
+        <v>124553015</v>
       </c>
       <c r="B35" t="n">
         <v>105676</v>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504726</v>
+        <v>504740</v>
       </c>
       <c r="R35" t="n">
-        <v>6611974</v>
+        <v>6612008</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4779,7 +4779,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553011</v>
+        <v>124553004</v>
       </c>
       <c r="B36" t="n">
         <v>105676</v>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504726</v>
+        <v>504750</v>
       </c>
       <c r="R36" t="n">
-        <v>6611959</v>
+        <v>6611973</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4890,7 +4890,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553004</v>
+        <v>124553034</v>
       </c>
       <c r="B37" t="n">
         <v>105676</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504750</v>
+        <v>504683</v>
       </c>
       <c r="R37" t="n">
-        <v>6611973</v>
+        <v>6611983</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5001,7 +5001,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553042</v>
+        <v>124553000</v>
       </c>
       <c r="B38" t="n">
         <v>105676</v>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5045,13 +5045,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504630</v>
+        <v>504774</v>
       </c>
       <c r="R38" t="n">
         <v>6611972</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5112,10 +5112,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553014</v>
+        <v>124553040</v>
       </c>
       <c r="B39" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5124,26 +5124,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5152,10 +5156,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504725</v>
+        <v>504638</v>
       </c>
       <c r="R39" t="n">
-        <v>6611991</v>
+        <v>6611981</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5192,7 +5196,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5201,7 +5205,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5220,7 +5223,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553015</v>
+        <v>124553011</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5264,10 +5267,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504740</v>
+        <v>504726</v>
       </c>
       <c r="R40" t="n">
-        <v>6612008</v>
+        <v>6611959</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5304,7 +5307,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5331,7 +5334,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553036</v>
+        <v>124553003</v>
       </c>
       <c r="B41" t="n">
         <v>105676</v>
@@ -5366,7 +5369,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5375,10 +5378,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504667</v>
+        <v>504753</v>
       </c>
       <c r="R41" t="n">
-        <v>6611981</v>
+        <v>6611982</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5415,7 +5418,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5442,7 +5445,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553032</v>
+        <v>124553016</v>
       </c>
       <c r="B42" t="n">
         <v>105676</v>
@@ -5477,7 +5480,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5486,10 +5489,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504686</v>
+        <v>504741</v>
       </c>
       <c r="R42" t="n">
-        <v>6611987</v>
+        <v>6612008</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5526,7 +5529,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5553,10 +5556,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553031</v>
+        <v>124553010</v>
       </c>
       <c r="B43" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5565,20 +5568,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5588,7 +5591,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5597,10 +5600,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504697</v>
+        <v>504732</v>
       </c>
       <c r="R43" t="n">
-        <v>6612016</v>
+        <v>6611958</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5633,11 +5636,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5664,10 +5662,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553017</v>
+        <v>124553014</v>
       </c>
       <c r="B44" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5676,27 +5674,23 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>1</t>
@@ -5708,10 +5702,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504749</v>
+        <v>504725</v>
       </c>
       <c r="R44" t="n">
-        <v>6612014</v>
+        <v>6611991</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5748,7 +5742,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5757,6 +5751,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5775,7 +5770,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553003</v>
+        <v>124553036</v>
       </c>
       <c r="B45" t="n">
         <v>105676</v>
@@ -5810,7 +5805,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5819,10 +5814,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504753</v>
+        <v>504667</v>
       </c>
       <c r="R45" t="n">
-        <v>6611982</v>
+        <v>6611981</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5859,7 +5854,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5886,7 +5881,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553037</v>
+        <v>124553002</v>
       </c>
       <c r="B46" t="n">
         <v>105676</v>
@@ -5921,7 +5916,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5930,10 +5925,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504667</v>
+        <v>504759</v>
       </c>
       <c r="R46" t="n">
-        <v>6611989</v>
+        <v>6611991</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5970,7 +5965,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5997,7 +5992,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553002</v>
+        <v>124553039</v>
       </c>
       <c r="B47" t="n">
         <v>105676</v>
@@ -6032,7 +6027,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6041,10 +6036,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504759</v>
+        <v>504635</v>
       </c>
       <c r="R47" t="n">
-        <v>6611991</v>
+        <v>6612001</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6081,7 +6076,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6108,10 +6103,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553010</v>
+        <v>124553043</v>
       </c>
       <c r="B48" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6120,20 +6115,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6143,7 +6138,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6152,10 +6147,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504732</v>
+        <v>504644</v>
       </c>
       <c r="R48" t="n">
-        <v>6611958</v>
+        <v>6611959</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6188,6 +6183,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6214,7 +6214,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553039</v>
+        <v>124553030</v>
       </c>
       <c r="B49" t="n">
         <v>105676</v>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504635</v>
+        <v>504720</v>
       </c>
       <c r="R49" t="n">
-        <v>6612001</v>
+        <v>6612011</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6325,7 +6325,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553033</v>
+        <v>124553005</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504688</v>
+        <v>504746</v>
       </c>
       <c r="R50" t="n">
-        <v>6611985</v>
+        <v>6611972</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6547,7 +6547,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553040</v>
+        <v>124553032</v>
       </c>
       <c r="B52" t="n">
         <v>105676</v>
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504638</v>
+        <v>504686</v>
       </c>
       <c r="R52" t="n">
-        <v>6611981</v>
+        <v>6611987</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6658,7 +6658,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553034</v>
+        <v>124553013</v>
       </c>
       <c r="B53" t="n">
         <v>105676</v>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504683</v>
+        <v>504727</v>
       </c>
       <c r="R53" t="n">
-        <v>6611983</v>
+        <v>6611975</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553043</v>
+        <v>124553033</v>
       </c>
       <c r="B54" t="n">
         <v>105676</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504644</v>
+        <v>504688</v>
       </c>
       <c r="R54" t="n">
-        <v>6611959</v>
+        <v>6611985</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553017</v>
+        <v>124553030</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504749</v>
+        <v>504720</v>
       </c>
       <c r="R29" t="n">
-        <v>6612014</v>
+        <v>6612011</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553012</v>
+        <v>124553035</v>
       </c>
       <c r="B30" t="n">
         <v>105676</v>
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504726</v>
+        <v>504665</v>
       </c>
       <c r="R30" t="n">
-        <v>6611974</v>
+        <v>6611970</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4224,7 +4224,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553037</v>
+        <v>124553016</v>
       </c>
       <c r="B31" t="n">
         <v>105676</v>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504667</v>
+        <v>504741</v>
       </c>
       <c r="R31" t="n">
-        <v>6611989</v>
+        <v>6612008</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,7 +4335,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553031</v>
+        <v>124553012</v>
       </c>
       <c r="B32" t="n">
         <v>105676</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504697</v>
+        <v>504726</v>
       </c>
       <c r="R32" t="n">
-        <v>6612016</v>
+        <v>6611974</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,7 +4446,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553042</v>
+        <v>124553036</v>
       </c>
       <c r="B33" t="n">
         <v>105676</v>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504630</v>
+        <v>504667</v>
       </c>
       <c r="R33" t="n">
-        <v>6611972</v>
+        <v>6611981</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4557,7 +4557,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553035</v>
+        <v>124553034</v>
       </c>
       <c r="B34" t="n">
         <v>105676</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504665</v>
+        <v>504683</v>
       </c>
       <c r="R34" t="n">
-        <v>6611970</v>
+        <v>6611983</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4668,7 +4668,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553015</v>
+        <v>124553017</v>
       </c>
       <c r="B35" t="n">
         <v>105676</v>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504740</v>
+        <v>504749</v>
       </c>
       <c r="R35" t="n">
-        <v>6612008</v>
+        <v>6612014</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4779,7 +4779,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553004</v>
+        <v>124553032</v>
       </c>
       <c r="B36" t="n">
         <v>105676</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504750</v>
+        <v>504686</v>
       </c>
       <c r="R36" t="n">
-        <v>6611973</v>
+        <v>6611987</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4890,7 +4890,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553034</v>
+        <v>124553040</v>
       </c>
       <c r="B37" t="n">
         <v>105676</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504683</v>
+        <v>504638</v>
       </c>
       <c r="R37" t="n">
-        <v>6611983</v>
+        <v>6611981</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5001,7 +5001,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553000</v>
+        <v>124553013</v>
       </c>
       <c r="B38" t="n">
         <v>105676</v>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5045,13 +5045,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504774</v>
+        <v>504727</v>
       </c>
       <c r="R38" t="n">
-        <v>6611972</v>
+        <v>6611975</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5112,7 +5112,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553040</v>
+        <v>124553011</v>
       </c>
       <c r="B39" t="n">
         <v>105676</v>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504638</v>
+        <v>504726</v>
       </c>
       <c r="R39" t="n">
-        <v>6611981</v>
+        <v>6611959</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5223,7 +5223,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553011</v>
+        <v>124553042</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504726</v>
+        <v>504630</v>
       </c>
       <c r="R40" t="n">
-        <v>6611959</v>
+        <v>6611972</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5334,10 +5334,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553003</v>
+        <v>124553014</v>
       </c>
       <c r="B41" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5346,30 +5346,26 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5378,10 +5374,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504753</v>
+        <v>504725</v>
       </c>
       <c r="R41" t="n">
-        <v>6611982</v>
+        <v>6611991</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5418,7 +5414,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5427,6 +5423,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5445,7 +5442,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553016</v>
+        <v>124553015</v>
       </c>
       <c r="B42" t="n">
         <v>105676</v>
@@ -5480,7 +5477,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5489,7 +5486,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504741</v>
+        <v>504740</v>
       </c>
       <c r="R42" t="n">
         <v>6612008</v>
@@ -5529,7 +5526,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5556,10 +5553,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553010</v>
+        <v>124553002</v>
       </c>
       <c r="B43" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5568,20 +5565,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5600,10 +5597,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504732</v>
+        <v>504759</v>
       </c>
       <c r="R43" t="n">
-        <v>6611958</v>
+        <v>6611991</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5636,6 +5633,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5662,10 +5664,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553014</v>
+        <v>124553033</v>
       </c>
       <c r="B44" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5674,26 +5676,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5702,10 +5708,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504725</v>
+        <v>504688</v>
       </c>
       <c r="R44" t="n">
-        <v>6611991</v>
+        <v>6611985</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5742,7 +5748,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5751,7 +5757,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5770,7 +5775,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553036</v>
+        <v>124553037</v>
       </c>
       <c r="B45" t="n">
         <v>105676</v>
@@ -5805,7 +5810,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5817,7 +5822,7 @@
         <v>504667</v>
       </c>
       <c r="R45" t="n">
-        <v>6611981</v>
+        <v>6611989</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5854,7 +5859,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5881,7 +5886,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553002</v>
+        <v>124553038</v>
       </c>
       <c r="B46" t="n">
         <v>105676</v>
@@ -5925,7 +5930,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504759</v>
+        <v>504663</v>
       </c>
       <c r="R46" t="n">
         <v>6611991</v>
@@ -5965,7 +5970,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5992,7 +5997,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553039</v>
+        <v>124553043</v>
       </c>
       <c r="B47" t="n">
         <v>105676</v>
@@ -6027,7 +6032,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6036,10 +6041,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504635</v>
+        <v>504644</v>
       </c>
       <c r="R47" t="n">
-        <v>6612001</v>
+        <v>6611959</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6103,7 +6108,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553043</v>
+        <v>124553004</v>
       </c>
       <c r="B48" t="n">
         <v>105676</v>
@@ -6138,7 +6143,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6147,10 +6152,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504644</v>
+        <v>504750</v>
       </c>
       <c r="R48" t="n">
-        <v>6611959</v>
+        <v>6611973</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6187,7 +6192,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6214,7 +6219,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553030</v>
+        <v>124553000</v>
       </c>
       <c r="B49" t="n">
         <v>105676</v>
@@ -6249,7 +6254,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6258,13 +6263,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504720</v>
+        <v>504774</v>
       </c>
       <c r="R49" t="n">
-        <v>6612011</v>
+        <v>6611972</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6298,7 +6303,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6325,7 +6330,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553005</v>
+        <v>124553003</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6360,7 +6365,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6369,10 +6374,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504746</v>
+        <v>504753</v>
       </c>
       <c r="R50" t="n">
-        <v>6611972</v>
+        <v>6611982</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6409,7 +6414,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6436,10 +6441,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553038</v>
+        <v>124553010</v>
       </c>
       <c r="B51" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6448,20 +6453,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6480,10 +6485,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504663</v>
+        <v>504732</v>
       </c>
       <c r="R51" t="n">
-        <v>6611991</v>
+        <v>6611958</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6516,11 +6521,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6547,7 +6547,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553032</v>
+        <v>124553039</v>
       </c>
       <c r="B52" t="n">
         <v>105676</v>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504686</v>
+        <v>504635</v>
       </c>
       <c r="R52" t="n">
-        <v>6611987</v>
+        <v>6612001</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6658,7 +6658,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553013</v>
+        <v>124553031</v>
       </c>
       <c r="B53" t="n">
         <v>105676</v>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504727</v>
+        <v>504697</v>
       </c>
       <c r="R53" t="n">
-        <v>6611975</v>
+        <v>6612016</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553033</v>
+        <v>124553005</v>
       </c>
       <c r="B54" t="n">
         <v>105676</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504688</v>
+        <v>504746</v>
       </c>
       <c r="R54" t="n">
-        <v>6611985</v>
+        <v>6611972</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553030</v>
+        <v>124553031</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504720</v>
+        <v>504697</v>
       </c>
       <c r="R29" t="n">
-        <v>6612011</v>
+        <v>6612016</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553035</v>
+        <v>124553037</v>
       </c>
       <c r="B30" t="n">
         <v>105676</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504665</v>
+        <v>504667</v>
       </c>
       <c r="R30" t="n">
-        <v>6611970</v>
+        <v>6611989</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4224,7 +4224,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553016</v>
+        <v>124553035</v>
       </c>
       <c r="B31" t="n">
         <v>105676</v>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504741</v>
+        <v>504665</v>
       </c>
       <c r="R31" t="n">
-        <v>6612008</v>
+        <v>6611970</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,7 +4335,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553012</v>
+        <v>124553002</v>
       </c>
       <c r="B32" t="n">
         <v>105676</v>
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504726</v>
+        <v>504759</v>
       </c>
       <c r="R32" t="n">
-        <v>6611974</v>
+        <v>6611991</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,7 +4446,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553036</v>
+        <v>124553034</v>
       </c>
       <c r="B33" t="n">
         <v>105676</v>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504667</v>
+        <v>504683</v>
       </c>
       <c r="R33" t="n">
-        <v>6611981</v>
+        <v>6611983</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4557,7 +4557,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553034</v>
+        <v>124553017</v>
       </c>
       <c r="B34" t="n">
         <v>105676</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504683</v>
+        <v>504749</v>
       </c>
       <c r="R34" t="n">
-        <v>6611983</v>
+        <v>6612014</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4668,7 +4668,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553017</v>
+        <v>124553039</v>
       </c>
       <c r="B35" t="n">
         <v>105676</v>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504749</v>
+        <v>504635</v>
       </c>
       <c r="R35" t="n">
-        <v>6612014</v>
+        <v>6612001</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4779,7 +4779,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553032</v>
+        <v>124553042</v>
       </c>
       <c r="B36" t="n">
         <v>105676</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504686</v>
+        <v>504630</v>
       </c>
       <c r="R36" t="n">
-        <v>6611987</v>
+        <v>6611972</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4890,7 +4890,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553040</v>
+        <v>124553015</v>
       </c>
       <c r="B37" t="n">
         <v>105676</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504638</v>
+        <v>504740</v>
       </c>
       <c r="R37" t="n">
-        <v>6611981</v>
+        <v>6612008</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5001,10 +5001,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553013</v>
+        <v>124553014</v>
       </c>
       <c r="B38" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5013,27 +5013,23 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>1</t>
@@ -5045,10 +5041,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504727</v>
+        <v>504725</v>
       </c>
       <c r="R38" t="n">
-        <v>6611975</v>
+        <v>6611991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5085,7 +5081,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5094,6 +5090,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5112,7 +5109,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553011</v>
+        <v>124553033</v>
       </c>
       <c r="B39" t="n">
         <v>105676</v>
@@ -5147,7 +5144,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5156,10 +5153,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504726</v>
+        <v>504688</v>
       </c>
       <c r="R39" t="n">
-        <v>6611959</v>
+        <v>6611985</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5196,7 +5193,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5223,7 +5220,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553042</v>
+        <v>124553005</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5258,7 +5255,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5267,7 +5264,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504630</v>
+        <v>504746</v>
       </c>
       <c r="R40" t="n">
         <v>6611972</v>
@@ -5307,7 +5304,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5334,10 +5331,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553014</v>
+        <v>124553040</v>
       </c>
       <c r="B41" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5346,26 +5343,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5374,10 +5375,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504725</v>
+        <v>504638</v>
       </c>
       <c r="R41" t="n">
-        <v>6611991</v>
+        <v>6611981</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5414,7 +5415,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5423,7 +5424,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553015</v>
+        <v>124553036</v>
       </c>
       <c r="B42" t="n">
         <v>105676</v>
@@ -5486,10 +5486,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504740</v>
+        <v>504667</v>
       </c>
       <c r="R42" t="n">
-        <v>6612008</v>
+        <v>6611981</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5553,7 +5553,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553002</v>
+        <v>124553004</v>
       </c>
       <c r="B43" t="n">
         <v>105676</v>
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504759</v>
+        <v>504750</v>
       </c>
       <c r="R43" t="n">
-        <v>6611991</v>
+        <v>6611973</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5664,10 +5664,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553033</v>
+        <v>124553010</v>
       </c>
       <c r="B44" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5676,20 +5676,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5708,10 +5708,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504688</v>
+        <v>504732</v>
       </c>
       <c r="R44" t="n">
-        <v>6611985</v>
+        <v>6611958</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5744,11 +5744,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5775,7 +5770,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553037</v>
+        <v>124553000</v>
       </c>
       <c r="B45" t="n">
         <v>105676</v>
@@ -5810,7 +5805,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5819,13 +5814,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504667</v>
+        <v>504774</v>
       </c>
       <c r="R45" t="n">
-        <v>6611989</v>
+        <v>6611972</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5859,7 +5854,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5886,7 +5881,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553038</v>
+        <v>124553030</v>
       </c>
       <c r="B46" t="n">
         <v>105676</v>
@@ -5921,7 +5916,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5930,10 +5925,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504663</v>
+        <v>504720</v>
       </c>
       <c r="R46" t="n">
-        <v>6611991</v>
+        <v>6612011</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5970,7 +5965,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5997,7 +5992,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553043</v>
+        <v>124553038</v>
       </c>
       <c r="B47" t="n">
         <v>105676</v>
@@ -6032,7 +6027,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6041,10 +6036,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504644</v>
+        <v>504663</v>
       </c>
       <c r="R47" t="n">
-        <v>6611959</v>
+        <v>6611991</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6081,7 +6076,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6108,7 +6103,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553004</v>
+        <v>124553012</v>
       </c>
       <c r="B48" t="n">
         <v>105676</v>
@@ -6152,10 +6147,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504750</v>
+        <v>504726</v>
       </c>
       <c r="R48" t="n">
-        <v>6611973</v>
+        <v>6611974</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6192,7 +6187,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6219,7 +6214,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553000</v>
+        <v>124553003</v>
       </c>
       <c r="B49" t="n">
         <v>105676</v>
@@ -6254,7 +6249,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6263,13 +6258,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504774</v>
+        <v>504753</v>
       </c>
       <c r="R49" t="n">
-        <v>6611972</v>
+        <v>6611982</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6303,7 +6298,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6330,7 +6325,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553003</v>
+        <v>124553011</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6365,7 +6360,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6374,10 +6369,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504753</v>
+        <v>504726</v>
       </c>
       <c r="R50" t="n">
-        <v>6611982</v>
+        <v>6611959</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6414,7 +6409,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6441,10 +6436,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553010</v>
+        <v>124553043</v>
       </c>
       <c r="B51" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6453,20 +6448,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6476,7 +6471,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6485,10 +6480,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504732</v>
+        <v>504644</v>
       </c>
       <c r="R51" t="n">
-        <v>6611958</v>
+        <v>6611959</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6521,6 +6516,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6547,7 +6547,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553039</v>
+        <v>124553032</v>
       </c>
       <c r="B52" t="n">
         <v>105676</v>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504635</v>
+        <v>504686</v>
       </c>
       <c r="R52" t="n">
-        <v>6612001</v>
+        <v>6611987</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6658,7 +6658,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553031</v>
+        <v>124553013</v>
       </c>
       <c r="B53" t="n">
         <v>105676</v>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504697</v>
+        <v>504727</v>
       </c>
       <c r="R53" t="n">
-        <v>6612016</v>
+        <v>6611975</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553005</v>
+        <v>124553016</v>
       </c>
       <c r="B54" t="n">
         <v>105676</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504746</v>
+        <v>504741</v>
       </c>
       <c r="R54" t="n">
-        <v>6611972</v>
+        <v>6612008</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4890,10 +4890,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553015</v>
+        <v>124553014</v>
       </c>
       <c r="B37" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4902,27 +4902,23 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>1</t>
@@ -4934,10 +4930,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504740</v>
+        <v>504725</v>
       </c>
       <c r="R37" t="n">
-        <v>6612008</v>
+        <v>6611991</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4974,7 +4970,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4983,6 +4979,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5001,10 +4998,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553014</v>
+        <v>124553015</v>
       </c>
       <c r="B38" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5013,23 +5010,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>1</t>
@@ -5041,10 +5042,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504725</v>
+        <v>504740</v>
       </c>
       <c r="R38" t="n">
-        <v>6611991</v>
+        <v>6612008</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5081,7 +5082,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5090,7 +5091,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553004</v>
+        <v>124553010</v>
       </c>
       <c r="B43" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5565,20 +5565,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504750</v>
+        <v>504732</v>
       </c>
       <c r="R43" t="n">
-        <v>6611973</v>
+        <v>6611958</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5633,11 +5633,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5664,10 +5659,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553010</v>
+        <v>124553004</v>
       </c>
       <c r="B44" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5676,20 +5671,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5708,10 +5703,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504732</v>
+        <v>504750</v>
       </c>
       <c r="R44" t="n">
-        <v>6611958</v>
+        <v>6611973</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5744,6 +5739,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -4002,7 +4002,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553031</v>
+        <v>124553011</v>
       </c>
       <c r="B29" t="n">
         <v>105676</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504697</v>
+        <v>504726</v>
       </c>
       <c r="R29" t="n">
-        <v>6612016</v>
+        <v>6611959</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553037</v>
+        <v>124553033</v>
       </c>
       <c r="B30" t="n">
         <v>105676</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504667</v>
+        <v>504688</v>
       </c>
       <c r="R30" t="n">
-        <v>6611989</v>
+        <v>6611985</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4224,7 +4224,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553035</v>
+        <v>124553034</v>
       </c>
       <c r="B31" t="n">
         <v>105676</v>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504665</v>
+        <v>504683</v>
       </c>
       <c r="R31" t="n">
-        <v>6611970</v>
+        <v>6611983</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,7 +4335,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553002</v>
+        <v>124553037</v>
       </c>
       <c r="B32" t="n">
         <v>105676</v>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504759</v>
+        <v>504667</v>
       </c>
       <c r="R32" t="n">
-        <v>6611991</v>
+        <v>6611989</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,7 +4446,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553034</v>
+        <v>124553031</v>
       </c>
       <c r="B33" t="n">
         <v>105676</v>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504683</v>
+        <v>504697</v>
       </c>
       <c r="R33" t="n">
-        <v>6611983</v>
+        <v>6612016</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4557,10 +4557,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553017</v>
+        <v>124553010</v>
       </c>
       <c r="B34" t="n">
-        <v>105676</v>
+        <v>103528</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4569,20 +4569,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504749</v>
+        <v>504732</v>
       </c>
       <c r="R34" t="n">
-        <v>6612014</v>
+        <v>6611958</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4637,11 +4637,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4779,7 +4774,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553042</v>
+        <v>124553005</v>
       </c>
       <c r="B36" t="n">
         <v>105676</v>
@@ -4814,7 +4809,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4823,7 +4818,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504630</v>
+        <v>504746</v>
       </c>
       <c r="R36" t="n">
         <v>6611972</v>
@@ -4863,7 +4858,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4890,10 +4885,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553014</v>
+        <v>124553042</v>
       </c>
       <c r="B37" t="n">
-        <v>102327</v>
+        <v>105676</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4902,26 +4897,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4930,10 +4929,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504725</v>
+        <v>504630</v>
       </c>
       <c r="R37" t="n">
-        <v>6611991</v>
+        <v>6611972</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4970,7 +4969,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4979,7 +4978,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4998,7 +4996,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553015</v>
+        <v>124553000</v>
       </c>
       <c r="B38" t="n">
         <v>105676</v>
@@ -5033,7 +5031,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5042,13 +5040,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504740</v>
+        <v>504774</v>
       </c>
       <c r="R38" t="n">
-        <v>6612008</v>
+        <v>6611972</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5082,7 +5080,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5109,7 +5107,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553033</v>
+        <v>124553032</v>
       </c>
       <c r="B39" t="n">
         <v>105676</v>
@@ -5144,7 +5142,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5153,10 +5151,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504688</v>
+        <v>504686</v>
       </c>
       <c r="R39" t="n">
-        <v>6611985</v>
+        <v>6611987</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5193,7 +5191,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5220,7 +5218,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553005</v>
+        <v>124553036</v>
       </c>
       <c r="B40" t="n">
         <v>105676</v>
@@ -5264,10 +5262,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504746</v>
+        <v>504667</v>
       </c>
       <c r="R40" t="n">
-        <v>6611972</v>
+        <v>6611981</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5304,7 +5302,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5331,7 +5329,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553040</v>
+        <v>124553015</v>
       </c>
       <c r="B41" t="n">
         <v>105676</v>
@@ -5366,7 +5364,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5375,10 +5373,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504638</v>
+        <v>504740</v>
       </c>
       <c r="R41" t="n">
-        <v>6611981</v>
+        <v>6612008</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5415,7 +5413,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5442,7 +5440,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553036</v>
+        <v>124553004</v>
       </c>
       <c r="B42" t="n">
         <v>105676</v>
@@ -5486,10 +5484,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504667</v>
+        <v>504750</v>
       </c>
       <c r="R42" t="n">
-        <v>6611981</v>
+        <v>6611973</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5526,7 +5524,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5553,10 +5551,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553010</v>
+        <v>124553040</v>
       </c>
       <c r="B43" t="n">
-        <v>103528</v>
+        <v>105676</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5565,20 +5563,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5588,7 +5586,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5597,10 +5595,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504732</v>
+        <v>504638</v>
       </c>
       <c r="R43" t="n">
-        <v>6611958</v>
+        <v>6611981</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5633,6 +5631,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>0,5 m höga</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5659,7 +5662,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553004</v>
+        <v>124553013</v>
       </c>
       <c r="B44" t="n">
         <v>105676</v>
@@ -5703,10 +5706,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504750</v>
+        <v>504727</v>
       </c>
       <c r="R44" t="n">
-        <v>6611973</v>
+        <v>6611975</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5743,7 +5746,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5770,7 +5773,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553000</v>
+        <v>124553002</v>
       </c>
       <c r="B45" t="n">
         <v>105676</v>
@@ -5805,7 +5808,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5814,13 +5817,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504774</v>
+        <v>504759</v>
       </c>
       <c r="R45" t="n">
-        <v>6611972</v>
+        <v>6611991</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5854,7 +5857,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5881,7 +5884,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553030</v>
+        <v>124553038</v>
       </c>
       <c r="B46" t="n">
         <v>105676</v>
@@ -5916,7 +5919,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5925,10 +5928,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504720</v>
+        <v>504663</v>
       </c>
       <c r="R46" t="n">
-        <v>6612011</v>
+        <v>6611991</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5965,7 +5968,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5992,10 +5995,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553038</v>
+        <v>124553014</v>
       </c>
       <c r="B47" t="n">
-        <v>105676</v>
+        <v>102327</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6004,27 +6007,23 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220785</v>
+        <v>225046</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>1</t>
@@ -6036,7 +6035,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504663</v>
+        <v>504725</v>
       </c>
       <c r="R47" t="n">
         <v>6611991</v>
@@ -6076,7 +6075,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6085,6 +6084,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553012</v>
+        <v>124553030</v>
       </c>
       <c r="B48" t="n">
         <v>105676</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504726</v>
+        <v>504720</v>
       </c>
       <c r="R48" t="n">
-        <v>6611974</v>
+        <v>6612011</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6214,7 +6214,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553003</v>
+        <v>124553016</v>
       </c>
       <c r="B49" t="n">
         <v>105676</v>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504753</v>
+        <v>504741</v>
       </c>
       <c r="R49" t="n">
-        <v>6611982</v>
+        <v>6612008</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6325,7 +6325,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553011</v>
+        <v>124553017</v>
       </c>
       <c r="B50" t="n">
         <v>105676</v>
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504726</v>
+        <v>504749</v>
       </c>
       <c r="R50" t="n">
-        <v>6611959</v>
+        <v>6612014</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6436,7 +6436,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553043</v>
+        <v>124553035</v>
       </c>
       <c r="B51" t="n">
         <v>105676</v>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504644</v>
+        <v>504665</v>
       </c>
       <c r="R51" t="n">
-        <v>6611959</v>
+        <v>6611970</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6547,7 +6547,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553032</v>
+        <v>124553003</v>
       </c>
       <c r="B52" t="n">
         <v>105676</v>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504686</v>
+        <v>504753</v>
       </c>
       <c r="R52" t="n">
-        <v>6611987</v>
+        <v>6611982</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6658,7 +6658,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553013</v>
+        <v>124553043</v>
       </c>
       <c r="B53" t="n">
         <v>105676</v>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504727</v>
+        <v>504644</v>
       </c>
       <c r="R53" t="n">
-        <v>6611975</v>
+        <v>6611959</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553016</v>
+        <v>124553012</v>
       </c>
       <c r="B54" t="n">
         <v>105676</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504741</v>
+        <v>504726</v>
       </c>
       <c r="R54" t="n">
-        <v>6612008</v>
+        <v>6611974</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6878,6 +6878,108 @@
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129463211</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98628</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Körartorp N-ut, Vstm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>504695</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6611980</v>
+      </c>
+      <c r="S55" t="n">
+        <v>75</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2013-07-07</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2013-07-07</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -6883,7 +6883,7 @@
         <v>129463211</v>
       </c>
       <c r="B55" t="n">
-        <v>98628</v>
+        <v>98630</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -6883,7 +6883,7 @@
         <v>129463211</v>
       </c>
       <c r="B55" t="n">
-        <v>98630</v>
+        <v>98634</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -6883,7 +6883,7 @@
         <v>129463211</v>
       </c>
       <c r="B55" t="n">
-        <v>98634</v>
+        <v>98642</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -6883,7 +6883,7 @@
         <v>129463211</v>
       </c>
       <c r="B55" t="n">
-        <v>98642</v>
+        <v>98645</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -6883,7 +6883,7 @@
         <v>129463211</v>
       </c>
       <c r="B55" t="n">
-        <v>98645</v>
+        <v>98674</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -6883,7 +6883,7 @@
         <v>129463211</v>
       </c>
       <c r="B55" t="n">
-        <v>98674</v>
+        <v>98686</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -6883,7 +6883,7 @@
         <v>129463211</v>
       </c>
       <c r="B55" t="n">
-        <v>98686</v>
+        <v>98687</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -6883,7 +6883,7 @@
         <v>129463211</v>
       </c>
       <c r="B55" t="n">
-        <v>98687</v>
+        <v>98692</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6980,6 +6980,396 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129833110</v>
+      </c>
+      <c r="B56" t="n">
+        <v>43245</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:35 Lejatorpet NO, Vstm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>504661</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6611899</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129833116</v>
+      </c>
+      <c r="B57" t="n">
+        <v>43245</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:35 Lejatorpet NO, Vstm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>504637</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6611943</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129833111</v>
+      </c>
+      <c r="B58" t="n">
+        <v>43245</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:35 Lejatorpet NO, Vstm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>504647</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6611946</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -6883,7 +6883,7 @@
         <v>129463211</v>
       </c>
       <c r="B55" t="n">
-        <v>98692</v>
+        <v>98696</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -6883,7 +6883,7 @@
         <v>129463211</v>
       </c>
       <c r="B55" t="n">
-        <v>98696</v>
+        <v>98698</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -6985,7 +6985,7 @@
         <v>129833110</v>
       </c>
       <c r="B56" t="n">
-        <v>43245</v>
+        <v>43248</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>129833116</v>
       </c>
       <c r="B57" t="n">
-        <v>43245</v>
+        <v>43248</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>129833111</v>
       </c>
       <c r="B58" t="n">
-        <v>43245</v>
+        <v>43248</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -6985,7 +6985,7 @@
         <v>129833110</v>
       </c>
       <c r="B56" t="n">
-        <v>43249</v>
+        <v>43334</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>129833116</v>
       </c>
       <c r="B57" t="n">
-        <v>43249</v>
+        <v>43334</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>129833111</v>
       </c>
       <c r="B58" t="n">
-        <v>43249</v>
+        <v>43334</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -6985,7 +6985,7 @@
         <v>129833110</v>
       </c>
       <c r="B56" t="n">
-        <v>43334</v>
+        <v>43249</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>129833116</v>
       </c>
       <c r="B57" t="n">
-        <v>43334</v>
+        <v>43249</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>129833111</v>
       </c>
       <c r="B58" t="n">
-        <v>43334</v>
+        <v>43249</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7370,6 +7370,112 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132075728</v>
+      </c>
+      <c r="B59" t="n">
+        <v>106739</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>504731</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6611960</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>1 dm dbh. 10 m hög. Verkar frisk.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -7375,7 +7375,7 @@
         <v>132075728</v>
       </c>
       <c r="B59" t="n">
-        <v>106739</v>
+        <v>106744</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -7375,7 +7375,7 @@
         <v>132075728</v>
       </c>
       <c r="B59" t="n">
-        <v>106744</v>
+        <v>106747</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -7375,7 +7375,7 @@
         <v>132075728</v>
       </c>
       <c r="B59" t="n">
-        <v>106788</v>
+        <v>106791</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -7375,7 +7375,7 @@
         <v>132075728</v>
       </c>
       <c r="B59" t="n">
-        <v>106791</v>
+        <v>106799</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -7375,7 +7375,7 @@
         <v>132075728</v>
       </c>
       <c r="B59" t="n">
-        <v>106799</v>
+        <v>106810</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -7375,7 +7375,7 @@
         <v>132075728</v>
       </c>
       <c r="B59" t="n">
-        <v>106810</v>
+        <v>106812</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -7375,7 +7375,7 @@
         <v>132075728</v>
       </c>
       <c r="B59" t="n">
-        <v>106812</v>
+        <v>106813</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -7375,7 +7375,7 @@
         <v>132075728</v>
       </c>
       <c r="B59" t="n">
-        <v>106813</v>
+        <v>106814</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -7375,7 +7375,7 @@
         <v>132075728</v>
       </c>
       <c r="B59" t="n">
-        <v>106814</v>
+        <v>106816</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>6890835</v>
       </c>
       <c r="B2" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -730,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504634.4682277355</v>
+        <v>504634</v>
       </c>
       <c r="R2" t="n">
-        <v>6611947.013201541</v>
+        <v>6611947</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,19 +758,9 @@
           <t>2013-07-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-07-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,67 +787,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60978242</v>
+        <v>96420243</v>
       </c>
       <c r="B3" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>720</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dammsjöhöjden, N om Leja, Vstm</t>
+          <t>Leja-Engbergatorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504733.6494764807</v>
+        <v>504754</v>
       </c>
       <c r="R3" t="n">
-        <v>6612006.284930941</v>
+        <v>6611939</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,22 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-08-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-08-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,76 +869,84 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Vägkant, blandskog</t>
+          <t>Lövrik granskog, kalkpåverkad örtmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Rolf Wedding</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60978243</v>
+        <v>96420244</v>
       </c>
       <c r="B4" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223246</v>
+        <v>720</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammsjöhöjden, N om Leja, Vstm</t>
+          <t>Leja-Engbergatorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504733.6494764807</v>
+        <v>504721</v>
       </c>
       <c r="R4" t="n">
-        <v>6612006.284930941</v>
+        <v>6611847</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,22 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-08-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-08-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,60 +984,65 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Vägkant, blandskog</t>
+          <t>Örtrik granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Rolf Wedding</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>60978249</v>
+        <v>113042761</v>
       </c>
       <c r="B5" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>720</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1090,24 +1052,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dammsjöhöjden, N om Leja, Vstm</t>
+          <t>Lejaområdet, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504664.2984474955</v>
+        <v>504764</v>
       </c>
       <c r="R5" t="n">
-        <v>6611985.471031853</v>
+        <v>6611875</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,22 +1091,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-08-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-08-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,71 +1107,70 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Blandskog, sank</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>60978254</v>
+        <v>113042762</v>
       </c>
       <c r="B6" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>720</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dammsjöhöjden, N om Leja, Vstm</t>
+          <t>Lejaområdet, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504644.5863594919</v>
+        <v>504732</v>
       </c>
       <c r="R6" t="n">
-        <v>6611955.114360242</v>
+        <v>6611890</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1251,22 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-08-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-08-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,88 +1213,67 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Vägkant, blandskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>60978250</v>
+        <v>96420245</v>
       </c>
       <c r="B7" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>1968</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dammsjöhöjden, N om Leja, Vstm</t>
+          <t>Leja-Engbergatorp, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504664.2984474955</v>
+        <v>504696</v>
       </c>
       <c r="R7" t="n">
-        <v>6611985.471031853</v>
+        <v>6611901</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1382,22 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2016-08-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2016-08-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,38 +1311,43 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Blandskog, sank</t>
+          <t>Örtrik granskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Rolf Wedding</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>60978244</v>
+        <v>96420229</v>
       </c>
       <c r="B8" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96337</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,51 +1355,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>2808</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grov husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hylocomiastrum pyrenaicum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Spruce) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dammsjöhöjden, N om Leja, Vstm</t>
+          <t>Leja-Engbergatorp, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504724.0278685726</v>
+        <v>504747</v>
       </c>
       <c r="R8" t="n">
-        <v>6612006.272775089</v>
+        <v>6611970</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1513,22 +1413,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2016-08-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2016-08-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,60 +1427,65 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Vägkant, blandskog</t>
+          <t>Lövrik barrskog, kalkpåverkad örtmark</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Rolf Wedding</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67478776</v>
+        <v>113042759</v>
       </c>
       <c r="B9" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100943</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1598,32 +1493,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Körartorp N-ut, Vstm</t>
+          <t>Lejaområdet, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504694.688981734</v>
+        <v>504722</v>
       </c>
       <c r="R9" t="n">
-        <v>6611980.45368302</v>
+        <v>6612034</v>
       </c>
       <c r="S9" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1647,27 +1534,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1975-06-22</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1975-06-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Insamlad av Jan Gustafsson och Lars-Ove Harrysson</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1682,49 +1554,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Claes Urban Eliasson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Claes Urban Eliasson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67478780</v>
+        <v>113042764</v>
       </c>
       <c r="B10" t="n">
-        <v>42719</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101298</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sotnätfjäril</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Melitaea diamina</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lang, 1789)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1732,28 +1599,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Körartorp N-ut, Vstm</t>
+          <t>Lejaområdet, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504694.688981734</v>
+        <v>504813</v>
       </c>
       <c r="R10" t="n">
-        <v>6611980.45368302</v>
+        <v>6611883</v>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1777,27 +1640,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1975-06-22</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1975-06-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Insamlad av Jan Gustafsson och Lars-Ove Harrysson</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1812,71 +1660,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Claes Urban Eliasson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Claes Urban Eliasson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94111699</v>
+        <v>96420242</v>
       </c>
       <c r="B11" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>5754</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lejaområdet, Vstm</t>
+          <t>Leja-Engbergatorp, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504704.9060215519</v>
+        <v>504646</v>
       </c>
       <c r="R11" t="n">
-        <v>6611909.690994641</v>
+        <v>6612010</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1903,22 +1740,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1927,80 +1754,98 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Rolf Wedding</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>94111695</v>
+        <v>67478776</v>
       </c>
       <c r="B12" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>100943</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lejaområdet, Vstm</t>
+          <t>Körartorp N-ut, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504647.1020774798</v>
+        <v>504695</v>
       </c>
       <c r="R12" t="n">
-        <v>6611968.261448621</v>
+        <v>6611980</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2024,22 +1869,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1975-06-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1975-06-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Insamlad av Jan Gustafsson och Lars-Ove Harrysson</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2054,49 +1894,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Claes Urban Eliasson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Via Claes Urban Eliasson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>94111694</v>
+        <v>105554976</v>
       </c>
       <c r="B13" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>100943</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2106,22 +1941,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lejaområdet, Vstm</t>
+          <t>Lejaområdet Yta 1:26 Lejatorpet, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504647.1008221983</v>
+        <v>504648</v>
       </c>
       <c r="R13" t="n">
-        <v>6611969.272519457</v>
+        <v>6611823</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2145,22 +1980,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2171,75 +2001,89 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>94111697</v>
+        <v>105555033</v>
       </c>
       <c r="B14" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>100943</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lejaområdet, Vstm</t>
+          <t>Lejaområdet Yta 1:23 Lejatorpet, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504744.3627001504</v>
+        <v>504735</v>
       </c>
       <c r="R14" t="n">
-        <v>6611944.117644719</v>
+        <v>6611804</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2266,22 +2110,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2292,31 +2131,45 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>94111698</v>
+        <v>113473535</v>
       </c>
       <c r="B15" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2324,161 +2177,176 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:26 Lejatorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>504644</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6611888</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
           <t>Fraxinus excelsior</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Lejaområdet, Vstm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>504764.1821365273</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6611889.54414948</v>
-      </c>
-      <c r="S15" t="n">
-        <v>25</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Lindesberg</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Linde</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96420244</v>
+        <v>120766219</v>
       </c>
       <c r="B16" t="n">
-        <v>88896</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>720</v>
+        <v>100943</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Leja-Engbergatorp, Vstm</t>
+          <t>Lejaområdet Yta 1:26 Lejatorpet, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504720.683897933</v>
+        <v>504650</v>
       </c>
       <c r="R16" t="n">
-        <v>6611847.022859184</v>
+        <v>6611829</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2502,22 +2370,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2526,48 +2384,47 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Rolf Wedding</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
+          <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96420165</v>
+        <v>120766220</v>
       </c>
       <c r="B17" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2575,161 +2432,181 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:26 Lejatorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>504640</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6611876</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
           <t>Fraxinus excelsior</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Leja-Engbergatorp, Vstm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>504660.8083903575</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6611941.48497284</v>
-      </c>
-      <c r="S17" t="n">
-        <v>25</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Lindesberg</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Linde</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ett 50-tal småträd och plantor</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rolf Wedding</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
+          <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96420242</v>
+        <v>129833110</v>
       </c>
       <c r="B18" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5754</v>
+        <v>100943</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Leja-Engbergatorp, Vstm</t>
+          <t>Lejaområdet Yta 1:35 Lejatorpet NO, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504646.0371837277</v>
+        <v>504661</v>
       </c>
       <c r="R18" t="n">
-        <v>6612010.219402254</v>
+        <v>6611899</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2753,22 +2630,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2777,90 +2644,99 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Rolf Wedding</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
+          <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96420229</v>
+        <v>129833111</v>
       </c>
       <c r="B19" t="n">
-        <v>93043</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2808</v>
+        <v>100943</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grov husmossa</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum pyrenaicum</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spruce) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Leja-Engbergatorp, Vstm</t>
+          <t>Lejaområdet Yta 1:35 Lejatorpet NO, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504747.3678115254</v>
+        <v>504647</v>
       </c>
       <c r="R19" t="n">
-        <v>6611970.409419734</v>
+        <v>6611946</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2884,22 +2760,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2908,48 +2774,47 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Lövrik barrskog, kalkpåverkad örtmark</t>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Rolf Wedding</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
+          <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96420164</v>
+        <v>129833116</v>
       </c>
       <c r="B20" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2957,161 +2822,181 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:35 Lejatorpet NO, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>504637</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6611943</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
           <t>Fraxinus excelsior</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Leja-Engbergatorp, Vstm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>504662.2753533482</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6611983.446374981</v>
-      </c>
-      <c r="S20" t="n">
-        <v>25</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Lindesberg</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Linde</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>1 medelålders</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Rolf Wedding</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
+          <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96420243</v>
+        <v>129833253</v>
       </c>
       <c r="B21" t="n">
-        <v>88896</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>720</v>
+        <v>100943</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Leja-Engbergatorp, Vstm</t>
+          <t>Lejaområdet Yta 1:26 Lejatorpet, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504753.4838370906</v>
+        <v>504619</v>
       </c>
       <c r="R21" t="n">
-        <v>6611939.579358214</v>
+        <v>6611921</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3135,22 +3020,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3159,89 +3034,99 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Lövrik granskog, kalkpåverkad örtmark</t>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Rolf Wedding</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Inger Holst</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
+          <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96420245</v>
+        <v>129833254</v>
       </c>
       <c r="B22" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1968</v>
+        <v>100943</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Leja-Engbergatorp, Vstm</t>
+          <t>Lejaområdet Yta 1:26 Lejatorpet, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>504696.3084094205</v>
+        <v>504620</v>
       </c>
       <c r="R22" t="n">
-        <v>6611900.580391653</v>
+        <v>6611922</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3265,22 +3150,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3289,86 +3164,98 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rolf Wedding</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Inger Holst</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
+          <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96420162</v>
+        <v>67478780</v>
       </c>
       <c r="B23" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220785</v>
+        <v>101298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Sotnätfjäril</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Melitaea diamina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Lang, 1789)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Leja-Engbergatorp, Vstm</t>
+          <t>Körartorp N-ut, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504801.2432476113</v>
+        <v>504695</v>
       </c>
       <c r="R23" t="n">
-        <v>6611817.297599059</v>
+        <v>6611980</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3392,27 +3279,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1975-06-22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1975-06-22</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1 medelålders+100-tals plantor</t>
+          <t>Insamlad av Jan Gustafsson och Lars-Ove Harrysson</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3427,53 +3304,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Rolf Wedding</t>
+          <t>Claes Urban Eliasson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Via Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113042762</v>
+        <v>60978242</v>
       </c>
       <c r="B24" t="n">
-        <v>89547</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>720</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3483,19 +3351,24 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lejaområdet, Vstm</t>
+          <t>Dammsjöhöjden, N om Leja, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504732</v>
+        <v>504734</v>
       </c>
       <c r="R24" t="n">
-        <v>6611889</v>
+        <v>6612006</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3522,12 +3395,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2016-08-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2016-08-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3538,31 +3411,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Vägkant, blandskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113042764</v>
+        <v>60978250</v>
       </c>
       <c r="B25" t="n">
-        <v>90972</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3570,21 +3443,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3594,19 +3467,24 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lejaområdet, Vstm</t>
+          <t>Dammsjöhöjden, N om Leja, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>504813</v>
+        <v>504664</v>
       </c>
       <c r="R25" t="n">
-        <v>6611883</v>
+        <v>6611985</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3633,12 +3511,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2016-08-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2016-08-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3649,53 +3527,53 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Blandskog, sank</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113042761</v>
+        <v>113042765</v>
       </c>
       <c r="B26" t="n">
-        <v>89547</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>720</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3705,7 +3583,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3714,10 +3592,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504763</v>
+        <v>504801</v>
       </c>
       <c r="R26" t="n">
-        <v>6611875</v>
+        <v>6611842</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3776,15 +3654,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113042765</v>
+        <v>113042948</v>
       </c>
       <c r="B27" t="n">
-        <v>97292</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3819,19 +3692,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lejaområdet, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504801</v>
+        <v>504769</v>
       </c>
       <c r="R27" t="n">
-        <v>6611842</v>
+        <v>6612020</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3869,6 +3745,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3887,15 +3764,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113042948</v>
+        <v>60978244</v>
       </c>
       <c r="B28" t="n">
-        <v>97292</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3903,49 +3775,51 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lejaområdet, Vstm</t>
+          <t>Dammsjöhöjden, N om Leja, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504769</v>
+        <v>504724</v>
       </c>
       <c r="R28" t="n">
-        <v>6612019</v>
+        <v>6612006</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3969,12 +3843,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2016-08-05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2016-08-05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3983,56 +3857,55 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Vägkant, blandskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124553011</v>
+        <v>60978249</v>
       </c>
       <c r="B29" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4040,16 +3913,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Dammsjöhöjden, N om Leja, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504726</v>
+        <v>504664</v>
       </c>
       <c r="R29" t="n">
-        <v>6611959</v>
+        <v>6611985</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4076,17 +3959,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2016-08-05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
+          <t>2016-08-05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4097,73 +3975,78 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Blandskog, sank</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124553033</v>
+        <v>94111676</v>
       </c>
       <c r="B30" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Lejaområdet, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504688</v>
+        <v>504616</v>
       </c>
       <c r="R30" t="n">
-        <v>6611985</v>
+        <v>6611986</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4187,17 +4070,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>10 m hög. 8 cm dbh. Frisk.</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4212,66 +4090,66 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124553034</v>
+        <v>94111697</v>
       </c>
       <c r="B31" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Lejaområdet, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504683</v>
+        <v>504745</v>
       </c>
       <c r="R31" t="n">
-        <v>6611983</v>
+        <v>6611944</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4298,17 +4176,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>0,5 m höga.</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4323,44 +4196,39 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124553037</v>
+        <v>60978254</v>
       </c>
       <c r="B32" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4368,21 +4236,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Dammsjöhöjden, N om Leja, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504667</v>
+        <v>504645</v>
       </c>
       <c r="R32" t="n">
-        <v>6611989</v>
+        <v>6611955</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4409,17 +4273,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2016-08-05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>1 m höga.</t>
+          <t>2016-08-05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4430,48 +4289,48 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Vägkant, blandskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124553031</v>
+        <v>94111695</v>
       </c>
       <c r="B33" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4481,19 +4340,24 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Lejaområdet, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504697</v>
+        <v>504647</v>
       </c>
       <c r="R33" t="n">
-        <v>6612016</v>
+        <v>6611968</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4520,17 +4384,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>0,4 m höga.</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4545,44 +4404,39 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124553010</v>
+        <v>94111698</v>
       </c>
       <c r="B34" t="n">
-        <v>103528</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4592,22 +4446,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Lejaområdet, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504732</v>
+        <v>504764</v>
       </c>
       <c r="R34" t="n">
-        <v>6611958</v>
+        <v>6611890</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4631,12 +4490,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4651,27 +4510,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124553039</v>
+        <v>96346546</v>
       </c>
       <c r="B35" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4701,16 +4555,21 @@
           <t>20</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Enbergatorp, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504635</v>
+        <v>504646</v>
       </c>
       <c r="R35" t="n">
-        <v>6612001</v>
+        <v>6611862</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4737,17 +4596,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>0 5-1 m höga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4774,15 +4633,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124553005</v>
+        <v>96346548</v>
       </c>
       <c r="B36" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4809,19 +4663,24 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Enbergatorp, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504746</v>
+        <v>504631</v>
       </c>
       <c r="R36" t="n">
-        <v>6611972</v>
+        <v>6611909</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4848,17 +4707,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>0,5 m höga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4885,15 +4744,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124553042</v>
+        <v>96346568</v>
       </c>
       <c r="B37" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4920,19 +4774,24 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Enbergatorp, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504630</v>
+        <v>504646</v>
       </c>
       <c r="R37" t="n">
-        <v>6611972</v>
+        <v>6611827</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4959,17 +4818,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>0,5-2 m höga. Dokumentation av asknätfjärilens värdväxter.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4996,15 +4855,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124553000</v>
+        <v>96420162</v>
       </c>
       <c r="B38" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5029,24 +4883,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Leja-Engbergatorp, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504774</v>
+        <v>504801</v>
       </c>
       <c r="R38" t="n">
-        <v>6611972</v>
+        <v>6611817</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5070,17 +4920,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
+          <t>1 medelålders+100-tals plantor</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5095,27 +4945,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Rolf Wedding</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124553032</v>
+        <v>96420164</v>
       </c>
       <c r="B39" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5140,24 +4989,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Leja-Engbergatorp, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504686</v>
+        <v>504662</v>
       </c>
       <c r="R39" t="n">
-        <v>6611987</v>
+        <v>6611983</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5181,17 +5026,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>0,4 m höga.</t>
+          <t>1 medelålders</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5206,27 +5051,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Rolf Wedding</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124553036</v>
+        <v>96420165</v>
       </c>
       <c r="B40" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5251,24 +5095,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Leja-Engbergatorp, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504667</v>
+        <v>504661</v>
       </c>
       <c r="R40" t="n">
-        <v>6611981</v>
+        <v>6611941</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5292,17 +5132,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+          <t>ett 50-tal småträd och plantor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5317,27 +5157,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Rolf Wedding</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124553015</v>
+        <v>113042758</v>
       </c>
       <c r="B41" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5364,19 +5203,24 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Leja, Vstm</t>
+          <t>Lejaområdet, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504740</v>
+        <v>504748</v>
       </c>
       <c r="R41" t="n">
-        <v>6612008</v>
+        <v>6612059</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5403,17 +5247,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5428,27 +5267,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124553004</v>
+        <v>124553000</v>
       </c>
       <c r="B42" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5475,7 +5309,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5484,13 +5318,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504750</v>
+        <v>504774</v>
       </c>
       <c r="R42" t="n">
-        <v>6611973</v>
+        <v>6611972</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5524,7 +5358,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
+          <t>10 till 20 m höga. 5 till 20 cm dbh. Verkar friska.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5551,15 +5385,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124553040</v>
+        <v>124553002</v>
       </c>
       <c r="B43" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5586,7 +5415,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5595,10 +5424,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504638</v>
+        <v>504759</v>
       </c>
       <c r="R43" t="n">
-        <v>6611981</v>
+        <v>6611991</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5635,7 +5464,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>0,5 m höga</t>
+          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5662,15 +5491,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124553013</v>
+        <v>124553003</v>
       </c>
       <c r="B44" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5697,7 +5521,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5706,10 +5530,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504727</v>
+        <v>504753</v>
       </c>
       <c r="R44" t="n">
-        <v>6611975</v>
+        <v>6611982</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5746,7 +5570,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5773,15 +5597,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124553002</v>
+        <v>124553004</v>
       </c>
       <c r="B45" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5817,10 +5636,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504759</v>
+        <v>504750</v>
       </c>
       <c r="R45" t="n">
-        <v>6611991</v>
+        <v>6611973</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5857,7 +5676,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>8 m hög. 5 cm dbh. Verkar frisk.</t>
+          <t>3 dm dbh. 20 m hög. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5884,15 +5703,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124553038</v>
+        <v>124553005</v>
       </c>
       <c r="B46" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5928,10 +5742,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504663</v>
+        <v>504746</v>
       </c>
       <c r="R46" t="n">
-        <v>6611991</v>
+        <v>6611972</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5968,7 +5782,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5995,35 +5809,34 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124553014</v>
+        <v>124553011</v>
       </c>
       <c r="B47" t="n">
-        <v>102327</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>1</t>
@@ -6035,10 +5848,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504725</v>
+        <v>504726</v>
       </c>
       <c r="R47" t="n">
-        <v>6611991</v>
+        <v>6611959</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6075,7 +5888,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Tillsynes frisk. 4 dm dbh.</t>
+          <t>2 dm dbh. 18 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6084,7 +5897,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6103,15 +5915,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124553030</v>
+        <v>124553012</v>
       </c>
       <c r="B48" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6138,7 +5945,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6147,10 +5954,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504720</v>
+        <v>504726</v>
       </c>
       <c r="R48" t="n">
-        <v>6612011</v>
+        <v>6611974</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6187,7 +5994,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6214,15 +6021,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124553016</v>
+        <v>124553013</v>
       </c>
       <c r="B49" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6249,7 +6051,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6258,10 +6060,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504741</v>
+        <v>504727</v>
       </c>
       <c r="R49" t="n">
-        <v>6612008</v>
+        <v>6611975</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6298,7 +6100,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>0,5 m höga.</t>
+          <t>2 dm dbh. 18 m hög. Trol askskottsjuka.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6325,15 +6127,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124553017</v>
+        <v>124553015</v>
       </c>
       <c r="B50" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6369,10 +6166,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504749</v>
+        <v>504740</v>
       </c>
       <c r="R50" t="n">
-        <v>6612014</v>
+        <v>6612008</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6409,7 +6206,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>15 m hög. 10 cm dbh. Frisk.</t>
+          <t>10 m hög. 7 cm dbh. Askskottsjuk.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6436,15 +6233,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124553035</v>
+        <v>124553016</v>
       </c>
       <c r="B51" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6471,7 +6263,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6480,10 +6272,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504665</v>
+        <v>504741</v>
       </c>
       <c r="R51" t="n">
-        <v>6611970</v>
+        <v>6612008</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6520,7 +6312,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+          <t>0,5 m höga.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6547,15 +6339,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124553003</v>
+        <v>124553017</v>
       </c>
       <c r="B52" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6582,7 +6369,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6591,10 +6378,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504753</v>
+        <v>504749</v>
       </c>
       <c r="R52" t="n">
-        <v>6611982</v>
+        <v>6612014</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6631,7 +6418,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>1 m höga.</t>
+          <t>15 m hög. 10 cm dbh. Frisk.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6658,15 +6445,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124553043</v>
+        <v>124553020</v>
       </c>
       <c r="B53" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6693,7 +6475,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6702,10 +6484,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504644</v>
+        <v>504699</v>
       </c>
       <c r="R53" t="n">
-        <v>6611959</v>
+        <v>6612035</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6742,7 +6524,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>3 m höga.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6769,15 +6551,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124553012</v>
+        <v>124553021</v>
       </c>
       <c r="B54" t="n">
-        <v>105676</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6804,7 +6581,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6813,10 +6590,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504726</v>
+        <v>504704</v>
       </c>
       <c r="R54" t="n">
-        <v>6611974</v>
+        <v>6612033</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6853,7 +6630,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>4 dm dbh. 20 m hög. Verkar frisk.</t>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6880,52 +6657,52 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129463211</v>
+        <v>124553023</v>
       </c>
       <c r="B55" t="n">
-        <v>98698</v>
+        <v>106813</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Körartorp N-ut, Vstm</t>
+          <t>Leja, Vstm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504695</v>
+        <v>504720</v>
       </c>
       <c r="R55" t="n">
-        <v>6611980</v>
+        <v>6612034</v>
       </c>
       <c r="S55" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6949,12 +6726,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2013-07-07</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2013-07-07</t>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6963,29 +6745,28 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Claes Urban Eliasson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Claes Urban Eliasson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129833110</v>
+        <v>124553026</v>
       </c>
       <c r="B56" t="n">
-        <v>43249</v>
+        <v>106813</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6993,48 +6774,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100943</v>
+        <v>220785</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:35 Lejatorpet NO, Vstm</t>
+          <t>Leja, Vstm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504661</v>
+        <v>504747</v>
       </c>
       <c r="R56" t="n">
-        <v>6611899</v>
+        <v>6612036</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7061,12 +6832,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>20 m hög. Antydan till askskottsjuka. 3 dm dbh.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7077,26 +6853,11 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -7104,18 +6865,14 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129833116</v>
+        <v>124553028</v>
       </c>
       <c r="B57" t="n">
-        <v>43249</v>
+        <v>106813</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7123,48 +6880,38 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100943</v>
+        <v>220785</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:35 Lejatorpet NO, Vstm</t>
+          <t>Leja, Vstm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504637</v>
+        <v>504748</v>
       </c>
       <c r="R57" t="n">
-        <v>6611943</v>
+        <v>6612035</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7191,12 +6938,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>20 m hög. Askskottsjuk. 4 dm dbh.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7207,26 +6959,11 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -7234,18 +6971,14 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129833111</v>
+        <v>124553030</v>
       </c>
       <c r="B58" t="n">
-        <v>43249</v>
+        <v>106813</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7253,48 +6986,38 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100943</v>
+        <v>220785</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:35 Lejatorpet NO, Vstm</t>
+          <t>Leja, Vstm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504647</v>
+        <v>504720</v>
       </c>
       <c r="R58" t="n">
-        <v>6611946</v>
+        <v>6612011</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7321,12 +7044,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>1 m höga.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7337,26 +7065,11 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -7364,18 +7077,14 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132075728</v>
+        <v>124553031</v>
       </c>
       <c r="B59" t="n">
-        <v>106816</v>
+        <v>106813</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7402,7 +7111,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7411,10 +7120,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504731</v>
+        <v>504697</v>
       </c>
       <c r="R59" t="n">
-        <v>6611960</v>
+        <v>6612016</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7451,7 +7160,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>1 dm dbh. 10 m hög. Verkar frisk.</t>
+          <t>0,4 m höga.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7475,6 +7184,2110 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>124553032</v>
+      </c>
+      <c r="B60" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>504686</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6611987</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>0,4 m höga.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>124553033</v>
+      </c>
+      <c r="B61" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>504688</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6611985</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>10 m hög. 8 cm dbh. Frisk.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>124553034</v>
+      </c>
+      <c r="B62" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>504683</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6611983</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>0,5 m höga.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>124553035</v>
+      </c>
+      <c r="B63" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>504665</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6611970</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>20 m hög. Kan ha askskottsjuka. Ca 4 dm dbh.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>124553036</v>
+      </c>
+      <c r="B64" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>504667</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6611981</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>20 m hög. Tillsynes frisk. Ca 5 dm dbh.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>124553037</v>
+      </c>
+      <c r="B65" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>504667</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6611989</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>1 m höga.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>124553038</v>
+      </c>
+      <c r="B66" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>504663</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6611991</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>20 m hög död askskottsjuk. 3 dm dbh.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>124553039</v>
+      </c>
+      <c r="B67" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>504635</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6612001</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>1 m höga</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>124553040</v>
+      </c>
+      <c r="B68" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>504638</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6611981</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>0,5 m höga</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>124553042</v>
+      </c>
+      <c r="B69" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>504630</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6611972</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>1 m höga</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>124553043</v>
+      </c>
+      <c r="B70" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>504644</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6611959</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>1 m höga</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>132075728</v>
+      </c>
+      <c r="B71" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>504731</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6611960</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>1 dm dbh. 10 m hög. Verkar frisk.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>94111694</v>
+      </c>
+      <c r="B72" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lejaområdet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>504647</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6611969</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2021-06-04</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2021-06-04</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>124553010</v>
+      </c>
+      <c r="B73" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>504732</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6611958</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>124553024</v>
+      </c>
+      <c r="B74" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>504722</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6612035</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>1 m höga.</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>94111675</v>
+      </c>
+      <c r="B75" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lejaområdet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>504617</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6611989</v>
+      </c>
+      <c r="S75" t="n">
+        <v>25</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2021-06-04</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2021-06-04</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>94111699</v>
+      </c>
+      <c r="B76" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lejaområdet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>504705</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6611910</v>
+      </c>
+      <c r="S76" t="n">
+        <v>25</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2021-06-04</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2021-06-04</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>60978243</v>
+      </c>
+      <c r="B77" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Dammsjöhöjden, N om Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>504734</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6612006</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2016-08-05</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2016-08-05</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Vägkant, blandskog</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129463211</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Körartorp N-ut, Vstm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>504695</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6611980</v>
+      </c>
+      <c r="S78" t="n">
+        <v>75</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2013-07-07</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2013-07-07</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Claes Urban Eliasson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>124553014</v>
+      </c>
+      <c r="B79" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Leja, Vstm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>504725</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6611991</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Tillsynes frisk. 4 dm dbh.</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58939-2023 artfynd.xlsx
+++ b/artfynd/A 58939-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6890835</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96420243</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96420244</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113042761</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113042762</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96420245</t>
         </is>
       </c>
     </row>
@@ -1457,6 +1492,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96420229</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113042759</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1669,6 +1714,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113042764</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1784,6 +1834,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96420242</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1903,6 +1958,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67478776</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2033,6 +2093,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105554976</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2163,6 +2228,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105555033</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2288,6 +2358,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113473535</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2418,6 +2493,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766219</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2548,6 +2628,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766220</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2678,6 +2763,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833110</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2808,6 +2898,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833111</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2938,6 +3033,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833116</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3068,6 +3168,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833253</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3198,6 +3303,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833254</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3313,6 +3423,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67478780</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3429,6 +3544,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60978242</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3545,6 +3665,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60978250</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3651,6 +3776,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113042765</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3761,6 +3891,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113042948</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3877,6 +4012,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60978244</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3993,6 +4133,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60978249</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4099,6 +4244,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94111676</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4205,6 +4355,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94111697</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4307,6 +4462,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60978254</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4413,6 +4573,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94111695</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4519,6 +4684,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94111698</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4630,6 +4800,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96346546</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4741,6 +4916,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96346548</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4852,6 +5032,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96346568</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4958,6 +5143,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96420162</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5064,6 +5254,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96420164</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5170,6 +5365,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96420165</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5276,6 +5476,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113042758</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5382,6 +5587,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553000</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5488,6 +5698,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553002</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5594,6 +5809,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553003</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5700,6 +5920,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553004</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5806,6 +6031,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553005</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5912,6 +6142,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553011</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6018,6 +6253,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553012</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6124,6 +6364,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553013</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6230,6 +6475,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553015</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6336,6 +6586,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553016</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6442,6 +6697,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553017</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6548,6 +6808,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553020</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6654,6 +6919,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553021</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6760,6 +7030,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553023</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6866,6 +7141,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553026</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6972,6 +7252,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553028</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7078,6 +7363,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553030</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7184,6 +7474,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553031</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7290,6 +7585,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553032</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7396,6 +7696,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553033</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7502,6 +7807,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553034</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7608,6 +7918,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553035</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7714,6 +8029,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553036</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7820,6 +8140,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553037</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7926,6 +8251,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553038</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8032,6 +8362,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553039</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8138,6 +8473,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553040</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8244,6 +8584,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553042</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8350,6 +8695,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553043</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8456,6 +8806,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132075728</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8562,6 +8917,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94111694</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8663,6 +9023,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553010</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8769,6 +9134,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553024</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8875,6 +9245,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94111675</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8981,6 +9356,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94111699</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9083,6 +9463,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60978243</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9185,6 +9570,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129463211</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9288,8 +9678,93 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124553014</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>